--- a/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
+++ b/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ezlo-VoiceAssistant\Deliverable\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7B508F-DD33-4082-B311-F3ACF102CCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77C85AA-0392-4AE6-B590-8A0DE3D7CFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="415">
   <si>
     <t>Component list</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C2, C37, C48, C49, C50, C51</t>
-  </si>
-  <si>
     <t>C3, C6, C53, C57</t>
   </si>
   <si>
@@ -71,12 +68,6 @@
     <t>C9, C22</t>
   </si>
   <si>
-    <t>C10, C12, C32, C36</t>
-  </si>
-  <si>
-    <t>C11, C13, C17, C18, C23, C35</t>
-  </si>
-  <si>
     <t>C14, C15</t>
   </si>
   <si>
@@ -107,27 +98,12 @@
     <t>C41, C42</t>
   </si>
   <si>
-    <t>C43, C45, C54, C55, C58, C66</t>
-  </si>
-  <si>
-    <t>C44</t>
-  </si>
-  <si>
     <t>C46</t>
   </si>
   <si>
     <t>C47</t>
   </si>
   <si>
-    <t>C52, C61, C62, C65</t>
-  </si>
-  <si>
-    <t>C56, C59</t>
-  </si>
-  <si>
-    <t>C63, C64</t>
-  </si>
-  <si>
     <t>D1, D2</t>
   </si>
   <si>
@@ -221,9 +197,6 @@
     <t>R29</t>
   </si>
   <si>
-    <t>R30</t>
-  </si>
-  <si>
     <t>R31</t>
   </si>
   <si>
@@ -299,9 +272,6 @@
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 100V X7R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 22PF 50V C0G/NP0 0402</t>
   </si>
   <si>
@@ -332,9 +302,6 @@
     <t>CAP CER 0.47UF 50V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 1UF 50V X7R 0603</t>
-  </si>
-  <si>
     <t>CAP SMD  2.7pF ±0.25pF 50V NPO 0603</t>
   </si>
   <si>
@@ -344,9 +311,6 @@
     <t>CAP CER 1000PF 25V C0G/NPO 0603</t>
   </si>
   <si>
-    <t>CAP CER 1UF 16V X5R 0603</t>
-  </si>
-  <si>
     <t>40V 500mV@2A 2A SMA(DO-214AC) Schottky Barrier Diodes (SBD) ROHS</t>
   </si>
   <si>
@@ -440,9 +404,6 @@
     <t>RES SMD 10 OHM 1% 1/4W 1206</t>
   </si>
   <si>
-    <t>RES SMD 100K OHM 0.1% 1/8W 0805</t>
-  </si>
-  <si>
     <t>RES SMD 1K OHM 0.5% 1/10W 0603</t>
   </si>
   <si>
@@ -569,9 +530,6 @@
     <t>Res1206</t>
   </si>
   <si>
-    <t>RES 0805</t>
-  </si>
-  <si>
     <t>Solder Bridge</t>
   </si>
   <si>
@@ -629,12 +587,6 @@
     <t>CL10A106MA8NRNC</t>
   </si>
   <si>
-    <t>CC0603KRX5R8BB105</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R0BB104</t>
-  </si>
-  <si>
     <t>04025A220FAT2A</t>
   </si>
   <si>
@@ -662,9 +614,6 @@
     <t>CL10A474KB8NNNC</t>
   </si>
   <si>
-    <t>UMK107AB7105KA-T</t>
-  </si>
-  <si>
     <t>CL10A105KA8NNNC</t>
   </si>
   <si>
@@ -674,15 +623,9 @@
     <t>CC0603BRNPO9BN4R7</t>
   </si>
   <si>
-    <t>CC0603FRNPO8BN102</t>
-  </si>
-  <si>
     <t>CC0603JRNPO8BN102</t>
   </si>
   <si>
-    <t>CC0603KRX5R7BB105</t>
-  </si>
-  <si>
     <t>ESD5451N-2/TR</t>
   </si>
   <si>
@@ -731,9 +674,6 @@
     <t>RT1206FRD0710RL</t>
   </si>
   <si>
-    <t>RT0805BRD07100KL</t>
-  </si>
-  <si>
     <t>RT0603DRD071KL</t>
   </si>
   <si>
@@ -782,9 +722,6 @@
     <t>ROQANG</t>
   </si>
   <si>
-    <t>Taiyo Yuden</t>
-  </si>
-  <si>
     <t>Sams</t>
   </si>
   <si>
@@ -914,9 +851,6 @@
     <t>4.7pF</t>
   </si>
   <si>
-    <t>1000pF</t>
-  </si>
-  <si>
     <t>1nF</t>
   </si>
   <si>
@@ -1085,12 +1019,6 @@
     <t>C96446</t>
   </si>
   <si>
-    <t>C14664</t>
-  </si>
-  <si>
-    <t>C113803</t>
-  </si>
-  <si>
     <t>C519410</t>
   </si>
   <si>
@@ -1118,9 +1046,6 @@
     <t>C327022</t>
   </si>
   <si>
-    <t>C106215</t>
-  </si>
-  <si>
     <t>C93225</t>
   </si>
   <si>
@@ -1163,9 +1088,6 @@
     <t>C326706</t>
   </si>
   <si>
-    <t>C122537</t>
-  </si>
-  <si>
     <t>C165964</t>
   </si>
   <si>
@@ -1202,9 +1124,6 @@
     <t>C390772</t>
   </si>
   <si>
-    <t>C105174</t>
-  </si>
-  <si>
     <t>C842786</t>
   </si>
   <si>
@@ -1262,12 +1181,6 @@
     <t>V332K0402X7R500NBT</t>
   </si>
   <si>
-    <t>0402X474K500CT</t>
-  </si>
-  <si>
-    <t>C2443204</t>
-  </si>
-  <si>
     <t>0603B102K250CT</t>
   </si>
   <si>
@@ -1341,6 +1254,27 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>C1, C2, C11, C13, C17, C18, C23, C35, C37, C48, C49, C50, C51</t>
+  </si>
+  <si>
+    <t>C10, C12, C32, C36, C43, C44, C45, C54, C55, C58, C63, C64, C66</t>
+  </si>
+  <si>
+    <t>C52, C56, C59, C61, C62, C65</t>
+  </si>
+  <si>
+    <t>0603F474M500NT</t>
+  </si>
+  <si>
+    <t>C1704</t>
+  </si>
+  <si>
+    <t>DZ254R-11-05-63</t>
+  </si>
+  <si>
+    <t>Need Custom Supplier Quote</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1286,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1514,13 +1448,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1533,8 +1460,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1565,32 +1515,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1839,21 +1765,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1881,7 +1792,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2039,21 +1950,33 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2078,99 +2001,60 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2515,7 +2399,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2549,15 +2433,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="65"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="69"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2568,7 +2452,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>433</v>
+        <v>404</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2593,7 +2477,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2607,7 +2491,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="66"/>
+      <c r="S3" s="70"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2618,7 +2502,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2632,7 +2516,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="67"/>
+      <c r="S4" s="71"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2657,7 +2541,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="67"/>
+      <c r="S5" s="71"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2678,7 +2562,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="67"/>
+      <c r="S6" s="71"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2699,7 +2583,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="67"/>
+      <c r="S7" s="71"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2720,7 +2604,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="67"/>
+      <c r="S8" s="71"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2728,109 +2612,109 @@
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="L9" s="31" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="S9" s="32" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="38">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="72" t="s">
-        <v>337</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="G10" s="60" t="s">
-        <v>195</v>
-      </c>
-      <c r="H10" s="59" t="s">
-        <v>242</v>
-      </c>
-      <c r="I10" s="59" t="s">
-        <v>335</v>
-      </c>
-      <c r="J10" s="59" t="s">
-        <v>345</v>
-      </c>
-      <c r="K10" s="59" t="s">
-        <v>277</v>
+      <c r="C10" s="60" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J10" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="K10" s="46" t="s">
+        <v>256</v>
       </c>
       <c r="L10" s="47">
-        <v>7</v>
-      </c>
-      <c r="M10" s="73">
+        <v>13</v>
+      </c>
+      <c r="M10" s="61">
         <f>L10*10</f>
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="N10" s="46">
-        <v>100</v>
-      </c>
-      <c r="O10" s="75" t="s">
-        <v>339</v>
+        <v>200</v>
+      </c>
+      <c r="O10" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P10" s="53">
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="Q10" s="53">
         <f>P10*N10</f>
-        <v>0.28999999999999998</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="R10" s="48"/>
       <c r="S10" s="49"/>
@@ -2838,58 +2722,58 @@
     <row r="11" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="38">
-        <f t="shared" ref="B11:B83" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B77" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="63" t="s">
-        <v>337</v>
+      <c r="C11" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J11" s="50" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="L11" s="51">
         <v>4</v>
       </c>
       <c r="M11" s="50">
-        <f t="shared" ref="M11:M74" si="1">L11*10</f>
+        <f t="shared" ref="M11:M68" si="1">L11*10</f>
         <v>40</v>
       </c>
       <c r="N11" s="50">
         <v>50</v>
       </c>
-      <c r="O11" s="78" t="s">
-        <v>339</v>
+      <c r="O11" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P11" s="54">
         <v>8.8599999999999998E-2</v>
       </c>
       <c r="Q11" s="54">
-        <f t="shared" ref="Q11:Q74" si="2">P11*N11</f>
+        <f t="shared" ref="Q11:Q68" si="2">P11*N11</f>
         <v>4.43</v>
       </c>
-      <c r="R11" s="85" t="s">
-        <v>405</v>
+      <c r="R11" s="64" t="s">
+        <v>378</v>
       </c>
       <c r="S11" s="52"/>
     </row>
@@ -2899,32 +2783,32 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="72" t="s">
-        <v>337</v>
+      <c r="C12" s="60" t="s">
+        <v>315</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="L12" s="47">
         <v>2</v>
@@ -2936,18 +2820,18 @@
       <c r="N12" s="46">
         <v>22</v>
       </c>
-      <c r="O12" s="75" t="s">
-        <v>339</v>
+      <c r="O12" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P12" s="53">
-        <v>0.40799999999999997</v>
+        <v>0.48549999999999999</v>
       </c>
       <c r="Q12" s="53">
         <f t="shared" si="2"/>
-        <v>8.9759999999999991</v>
-      </c>
-      <c r="R12" s="86" t="s">
-        <v>406</v>
+        <v>10.680999999999999</v>
+      </c>
+      <c r="R12" s="65" t="s">
+        <v>379</v>
       </c>
       <c r="S12" s="48"/>
     </row>
@@ -2957,32 +2841,32 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="63" t="s">
-        <v>337</v>
+      <c r="C13" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>196</v>
+        <v>142</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>182</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -2994,8 +2878,8 @@
       <c r="N13" s="50">
         <v>100</v>
       </c>
-      <c r="O13" s="78" t="s">
-        <v>339</v>
+      <c r="O13" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P13" s="54">
         <v>2.5000000000000001E-3</v>
@@ -3004,7 +2888,7 @@
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
-      <c r="R13" s="52"/>
+      <c r="R13" s="64"/>
       <c r="S13" s="52"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3013,32 +2897,32 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="72" t="s">
-        <v>337</v>
+      <c r="C14" s="60" t="s">
+        <v>315</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>197</v>
+        <v>145</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>183</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="L14" s="47">
         <v>1</v>
@@ -3050,8 +2934,8 @@
       <c r="N14" s="46">
         <v>100</v>
       </c>
-      <c r="O14" s="75" t="s">
-        <v>339</v>
+      <c r="O14" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P14" s="53">
         <v>3.0999999999999999E-3</v>
@@ -3060,7 +2944,7 @@
         <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
-      <c r="R14" s="48"/>
+      <c r="R14" s="65"/>
       <c r="S14" s="48"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3069,32 +2953,32 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="63" t="s">
-        <v>337</v>
+      <c r="C15" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="G15" s="51" t="s">
-        <v>198</v>
+        <v>142</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>184</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -3106,8 +2990,8 @@
       <c r="N15" s="50">
         <v>40</v>
       </c>
-      <c r="O15" s="78" t="s">
-        <v>339</v>
+      <c r="O15" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P15" s="54">
         <v>1.4200000000000001E-2</v>
@@ -3116,7 +3000,7 @@
         <f t="shared" si="2"/>
         <v>0.56800000000000006</v>
       </c>
-      <c r="R15" s="52"/>
+      <c r="R15" s="64"/>
       <c r="S15" s="52"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3125,52 +3009,54 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="72" t="s">
-        <v>337</v>
-      </c>
-      <c r="D16" s="87" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="88" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="87" t="s">
-        <v>155</v>
-      </c>
-      <c r="G16" s="88" t="s">
-        <v>199</v>
-      </c>
-      <c r="H16" s="87" t="s">
-        <v>242</v>
-      </c>
-      <c r="I16" s="87"/>
-      <c r="J16" s="87" t="s">
-        <v>351</v>
-      </c>
-      <c r="K16" s="87" t="s">
-        <v>283</v>
+      <c r="C16" s="60" t="s">
+        <v>315</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="I16" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J16" s="46" t="s">
+        <v>380</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>263</v>
       </c>
       <c r="L16" s="47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16" s="46">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N16" s="46">
-        <v>50</v>
-      </c>
-      <c r="O16" s="75" t="s">
-        <v>339</v>
+        <v>100</v>
+      </c>
+      <c r="O16" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P16" s="53">
-        <v>5.7999999999999996E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q16" s="53">
         <f t="shared" si="2"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="R16" s="48"/>
+        <v>0.1</v>
+      </c>
+      <c r="R16" s="65"/>
       <c r="S16" s="48"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3179,52 +3065,54 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="63" t="s">
-        <v>337</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="61" t="s">
-        <v>155</v>
-      </c>
-      <c r="G17" s="62" t="s">
-        <v>200</v>
-      </c>
-      <c r="H17" s="61" t="s">
-        <v>242</v>
-      </c>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61" t="s">
-        <v>352</v>
-      </c>
-      <c r="K17" s="61" t="s">
-        <v>277</v>
+      <c r="C17" s="59" t="s">
+        <v>315</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="I17" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="J17" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="K17" s="50" t="s">
+        <v>264</v>
       </c>
       <c r="L17" s="51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M17" s="50">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="N17" s="50">
         <v>100</v>
       </c>
-      <c r="O17" s="78" t="s">
-        <v>339</v>
+      <c r="O17" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P17" s="54">
-        <v>5.7000000000000002E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="Q17" s="54">
         <f t="shared" si="2"/>
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="R17" s="52"/>
+        <v>0.32</v>
+      </c>
+      <c r="R17" s="64"/>
       <c r="S17" s="52"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3233,54 +3121,54 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="72" t="s">
-        <v>337</v>
+      <c r="C18" s="60" t="s">
+        <v>315</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="47" t="s">
-        <v>201</v>
+        <v>142</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>187</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>407</v>
+        <v>316</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="L18" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="46">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N18" s="46">
         <v>20</v>
       </c>
-      <c r="N18" s="46">
-        <v>100</v>
-      </c>
-      <c r="O18" s="75" t="s">
-        <v>339</v>
+      <c r="O18" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P18" s="53">
-        <v>1E-3</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="Q18" s="53">
         <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="R18" s="48"/>
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="R18" s="65"/>
       <c r="S18" s="48"/>
     </row>
     <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3289,32 +3177,32 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="63" t="s">
-        <v>337</v>
+      <c r="C19" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>202</v>
+        <v>146</v>
+      </c>
+      <c r="G19" s="80" t="s">
+        <v>188</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -3326,17 +3214,17 @@
       <c r="N19" s="50">
         <v>100</v>
       </c>
-      <c r="O19" s="78" t="s">
-        <v>339</v>
+      <c r="O19" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P19" s="54">
-        <v>3.2000000000000002E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="Q19" s="54">
         <f t="shared" si="2"/>
-        <v>0.32</v>
-      </c>
-      <c r="R19" s="52"/>
+        <v>0.2</v>
+      </c>
+      <c r="R19" s="64"/>
       <c r="S19" s="52"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3345,32 +3233,32 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="72" t="s">
-        <v>337</v>
+      <c r="C20" s="60" t="s">
+        <v>315</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="G20" s="47" t="s">
-        <v>203</v>
+        <v>142</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>189</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="L20" s="47">
         <v>1</v>
@@ -3380,19 +3268,19 @@
         <v>10</v>
       </c>
       <c r="N20" s="46">
-        <v>20</v>
-      </c>
-      <c r="O20" s="75" t="s">
-        <v>339</v>
+        <v>100</v>
+      </c>
+      <c r="O20" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P20" s="53">
-        <v>1.7899999999999999E-2</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q20" s="53">
         <f t="shared" si="2"/>
-        <v>0.35799999999999998</v>
-      </c>
-      <c r="R20" s="48"/>
+        <v>0.21</v>
+      </c>
+      <c r="R20" s="65"/>
       <c r="S20" s="48"/>
     </row>
     <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3401,54 +3289,54 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="63" t="s">
-        <v>337</v>
+      <c r="C21" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="G21" s="82" t="s">
-        <v>204</v>
+        <v>142</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>190</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>409</v>
+        <v>313</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>408</v>
+        <v>331</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="L21" s="51">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M21" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="N21" s="50">
         <v>100</v>
       </c>
-      <c r="O21" s="78" t="s">
-        <v>339</v>
+      <c r="O21" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P21" s="54">
-        <v>2E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="Q21" s="54">
         <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="R21" s="52"/>
+        <v>0.74</v>
+      </c>
+      <c r="R21" s="64"/>
       <c r="S21" s="52"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3457,54 +3345,54 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="72" t="s">
-        <v>337</v>
+      <c r="C22" s="60" t="s">
+        <v>315</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>205</v>
+        <v>142</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>191</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="K22" s="46" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="L22" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="46">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N22" s="46">
         <v>100</v>
       </c>
-      <c r="O22" s="75" t="s">
-        <v>339</v>
+      <c r="O22" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P22" s="53">
-        <v>2.0999999999999999E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="Q22" s="53">
         <f t="shared" si="2"/>
-        <v>0.21</v>
-      </c>
-      <c r="R22" s="48"/>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="R22" s="65"/>
       <c r="S22" s="48"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3513,54 +3401,54 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="63" t="s">
-        <v>337</v>
+      <c r="C23" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>206</v>
+        <v>148</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>192</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="L23" s="51">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M23" s="50">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N23" s="50">
-        <v>100</v>
-      </c>
-      <c r="O23" s="78" t="s">
-        <v>339</v>
+        <v>22</v>
+      </c>
+      <c r="O23" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P23" s="54">
-        <v>7.4000000000000003E-3</v>
+        <v>0.19009999999999999</v>
       </c>
       <c r="Q23" s="54">
         <f t="shared" si="2"/>
-        <v>0.74</v>
-      </c>
-      <c r="R23" s="52"/>
+        <v>4.1821999999999999</v>
+      </c>
+      <c r="R23" s="64"/>
       <c r="S23" s="52"/>
     </row>
     <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3569,32 +3457,32 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="72" t="s">
-        <v>337</v>
+      <c r="C24" s="60" t="s">
+        <v>315</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>207</v>
+        <v>311</v>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>310</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="K24" s="46" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="L24" s="47">
         <v>2</v>
@@ -3604,19 +3492,19 @@
         <v>20</v>
       </c>
       <c r="N24" s="46">
-        <v>100</v>
-      </c>
-      <c r="O24" s="75" t="s">
-        <v>339</v>
+        <v>40</v>
+      </c>
+      <c r="O24" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P24" s="53">
-        <v>2.8E-3</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="Q24" s="53">
         <f t="shared" si="2"/>
-        <v>0.27999999999999997</v>
-      </c>
-      <c r="R24" s="48"/>
+        <v>1.1600000000000001</v>
+      </c>
+      <c r="R24" s="65"/>
       <c r="S24" s="48"/>
     </row>
     <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3625,32 +3513,32 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="63" t="s">
-        <v>337</v>
+      <c r="C25" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>208</v>
+        <v>142</v>
+      </c>
+      <c r="G25" s="80" t="s">
+        <v>193</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>335</v>
+        <v>411</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>357</v>
+        <v>412</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="L25" s="51">
         <v>2</v>
@@ -3660,187 +3548,187 @@
         <v>20</v>
       </c>
       <c r="N25" s="50">
-        <v>22</v>
-      </c>
-      <c r="O25" s="78" t="s">
-        <v>339</v>
+        <v>50</v>
+      </c>
+      <c r="O25" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P25" s="54">
-        <v>0.19009999999999999</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="Q25" s="54">
         <f t="shared" si="2"/>
-        <v>4.1821999999999999</v>
-      </c>
-      <c r="R25" s="52"/>
+        <v>0.59500000000000008</v>
+      </c>
+      <c r="R25" s="64"/>
       <c r="S25" s="52"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="38">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="72" t="s">
-        <v>337</v>
+      <c r="C26" s="60" t="s">
+        <v>315</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>23</v>
+        <v>409</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>333</v>
+        <v>142</v>
       </c>
       <c r="G26" s="46" t="s">
-        <v>332</v>
+        <v>194</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="I26" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J26" s="46" t="s">
         <v>335</v>
       </c>
-      <c r="J26" s="46" t="s">
-        <v>358</v>
-      </c>
       <c r="K26" s="46" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="L26" s="47">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M26" s="46">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="N26" s="46">
-        <v>40</v>
-      </c>
-      <c r="O26" s="75" t="s">
-        <v>339</v>
+        <v>150</v>
+      </c>
+      <c r="O26" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P26" s="53">
-        <v>2.9000000000000001E-2</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="Q26" s="53">
         <f t="shared" si="2"/>
-        <v>1.1600000000000001</v>
-      </c>
-      <c r="R26" s="48"/>
+        <v>0.63</v>
+      </c>
+      <c r="R26" s="65"/>
       <c r="S26" s="48"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="63" t="s">
-        <v>337</v>
+      <c r="C27" s="59" t="s">
+        <v>315</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="G27" s="82" t="s">
-        <v>209</v>
+        <v>147</v>
+      </c>
+      <c r="G27" s="50" t="s">
+        <v>195</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>410</v>
+        <v>313</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>411</v>
+        <v>336</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="L27" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" s="50">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N27" s="50">
         <v>50</v>
       </c>
-      <c r="O27" s="78" t="s">
-        <v>339</v>
+      <c r="O27" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P27" s="54">
-        <v>1.23E-2</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="Q27" s="54">
         <f t="shared" si="2"/>
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="R27" s="52"/>
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="R27" s="64"/>
       <c r="S27" s="52"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="38">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="60" t="s">
+        <v>315</v>
+      </c>
+      <c r="D28" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="H28" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="I28" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J28" s="46" t="s">
         <v>337</v>
       </c>
-      <c r="D28" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="88" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="87" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="88" t="s">
-        <v>210</v>
-      </c>
-      <c r="H28" s="87" t="s">
-        <v>250</v>
-      </c>
-      <c r="I28" s="87" t="s">
-        <v>335</v>
-      </c>
-      <c r="J28" s="87" t="s">
-        <v>390</v>
-      </c>
-      <c r="K28" s="87" t="s">
-        <v>283</v>
+      <c r="K28" s="46" t="s">
+        <v>272</v>
       </c>
       <c r="L28" s="47">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M28" s="46">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="N28" s="46">
-        <v>80</v>
-      </c>
-      <c r="O28" s="75" t="s">
-        <v>339</v>
+        <v>50</v>
+      </c>
+      <c r="O28" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P28" s="53">
-        <v>3.6900000000000002E-2</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="Q28" s="53">
         <f t="shared" si="2"/>
-        <v>2.952</v>
-      </c>
-      <c r="R28" s="48"/>
+        <v>0.26</v>
+      </c>
+      <c r="R28" s="65"/>
       <c r="S28" s="48"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3849,144 +3737,144 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="63" t="s">
-        <v>337</v>
-      </c>
-      <c r="D29" s="89" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="90" t="s">
-        <v>88</v>
-      </c>
-      <c r="F29" s="89" t="s">
-        <v>155</v>
-      </c>
-      <c r="G29" s="90" t="s">
-        <v>211</v>
-      </c>
-      <c r="H29" s="89" t="s">
-        <v>251</v>
-      </c>
-      <c r="I29" s="89" t="s">
-        <v>335</v>
-      </c>
-      <c r="J29" s="89" t="s">
-        <v>359</v>
-      </c>
-      <c r="K29" s="89" t="s">
-        <v>283</v>
+      <c r="C29" s="59" t="s">
+        <v>315</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="I29" s="50" t="s">
+        <v>383</v>
+      </c>
+      <c r="J29" s="50" t="s">
+        <v>384</v>
+      </c>
+      <c r="K29" s="50" t="s">
+        <v>273</v>
       </c>
       <c r="L29" s="51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M29" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="N29" s="50">
-        <v>50</v>
-      </c>
-      <c r="O29" s="78" t="s">
-        <v>339</v>
+        <v>100</v>
+      </c>
+      <c r="O29" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P29" s="54">
-        <v>4.1999999999999997E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="Q29" s="54">
         <f t="shared" si="2"/>
-        <v>0.21</v>
-      </c>
-      <c r="R29" s="52"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="R29" s="64"/>
       <c r="S29" s="52"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="38">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="72" t="s">
-        <v>337</v>
+      <c r="C30" s="60" t="s">
+        <v>312</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="G30" s="47" t="s">
-        <v>212</v>
+        <v>149</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>274</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="I30" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K30" s="46" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="L30" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="46">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N30" s="46">
-        <v>50</v>
-      </c>
-      <c r="O30" s="75" t="s">
-        <v>339</v>
+        <v>40</v>
+      </c>
+      <c r="O30" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P30" s="53">
-        <v>6.4999999999999997E-3</v>
+        <v>2.52E-2</v>
       </c>
       <c r="Q30" s="53">
         <f t="shared" si="2"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="R30" s="48"/>
+        <v>1.008</v>
+      </c>
+      <c r="R30" s="65"/>
       <c r="S30" s="48"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="63" t="s">
-        <v>337</v>
+      <c r="C31" s="59" t="s">
+        <v>312</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>213</v>
+        <v>366</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>150</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="L31" s="51">
         <v>1</v>
@@ -3996,277 +3884,277 @@
         <v>10</v>
       </c>
       <c r="N31" s="50">
-        <v>50</v>
-      </c>
-      <c r="O31" s="78" t="s">
-        <v>339</v>
+        <v>20</v>
+      </c>
+      <c r="O31" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P31" s="54">
-        <v>5.1999999999999998E-3</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="Q31" s="54">
         <f t="shared" si="2"/>
-        <v>0.26</v>
-      </c>
-      <c r="R31" s="52"/>
+        <v>0.98</v>
+      </c>
+      <c r="R31" s="64"/>
       <c r="S31" s="52"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="38">
-        <f>ROW(B32) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="72" t="s">
-        <v>337</v>
-      </c>
-      <c r="D32" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="92" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="91" t="s">
-        <v>155</v>
-      </c>
-      <c r="G32" s="92" t="s">
-        <v>214</v>
-      </c>
-      <c r="H32" s="91" t="s">
-        <v>242</v>
-      </c>
-      <c r="I32" s="91" t="s">
-        <v>412</v>
-      </c>
-      <c r="J32" s="91" t="s">
-        <v>413</v>
-      </c>
-      <c r="K32" s="91" t="s">
-        <v>294</v>
+      <c r="C32" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="D32" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="G32" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="H32" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="I32" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J32" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="K32" s="46" t="s">
+        <v>313</v>
       </c>
       <c r="L32" s="47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M32" s="46">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N32" s="46">
         <v>50</v>
       </c>
-      <c r="O32" s="75" t="s">
-        <v>339</v>
+      <c r="O32" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P32" s="53">
-        <v>4.4999999999999997E-3</v>
+        <v>1.95E-2</v>
       </c>
       <c r="Q32" s="53">
         <f t="shared" si="2"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="R32" s="48"/>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="R32" s="65"/>
       <c r="S32" s="48"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="63" t="s">
-        <v>337</v>
-      </c>
-      <c r="D33" s="93" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="94" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="93" t="s">
-        <v>155</v>
-      </c>
-      <c r="G33" s="94" t="s">
-        <v>215</v>
-      </c>
-      <c r="H33" s="93" t="s">
-        <v>242</v>
-      </c>
-      <c r="I33" s="93" t="s">
-        <v>412</v>
-      </c>
-      <c r="J33" s="93" t="s">
-        <v>413</v>
-      </c>
-      <c r="K33" s="93" t="s">
-        <v>295</v>
+      <c r="C33" s="59" t="s">
+        <v>395</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>311</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>234</v>
+      </c>
+      <c r="I33" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="J33" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="K33" s="50" t="s">
+        <v>313</v>
       </c>
       <c r="L33" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="50">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N33" s="50">
-        <v>50</v>
-      </c>
-      <c r="O33" s="78" t="s">
-        <v>339</v>
+        <v>15</v>
+      </c>
+      <c r="O33" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P33" s="54">
-        <v>4.4999999999999997E-3</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="Q33" s="54">
         <f t="shared" si="2"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="R33" s="52"/>
+        <v>1.3125</v>
+      </c>
+      <c r="R33" s="64"/>
       <c r="S33" s="52"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="38">
-        <f>ROW(B34) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="72" t="s">
-        <v>337</v>
-      </c>
-      <c r="D34" s="87" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="88" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" s="87" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" s="88" t="s">
-        <v>216</v>
-      </c>
-      <c r="H34" s="87" t="s">
-        <v>242</v>
-      </c>
-      <c r="I34" s="87" t="s">
-        <v>335</v>
-      </c>
-      <c r="J34" s="87" t="s">
-        <v>362</v>
-      </c>
-      <c r="K34" s="87" t="s">
-        <v>283</v>
+      <c r="C34" s="60" t="s">
+        <v>396</v>
+      </c>
+      <c r="D34" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="G34" s="81" t="s">
+        <v>199</v>
+      </c>
+      <c r="H34" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="I34" s="46" t="s">
+        <v>413</v>
+      </c>
+      <c r="J34" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="K34" s="46" t="s">
+        <v>313</v>
       </c>
       <c r="L34" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="46">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N34" s="46">
         <v>20</v>
       </c>
-      <c r="N34" s="46">
-        <v>50</v>
-      </c>
-      <c r="O34" s="75" t="s">
-        <v>339</v>
+      <c r="O34" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P34" s="53">
-        <v>6.1999999999999998E-3</v>
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="Q34" s="53">
         <f t="shared" si="2"/>
-        <v>0.31</v>
-      </c>
-      <c r="R34" s="48"/>
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="R34" s="65"/>
       <c r="S34" s="48"/>
     </row>
-    <row r="35" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="63" t="s">
-        <v>334</v>
+      <c r="C35" s="59" t="s">
+        <v>395</v>
       </c>
       <c r="D35" s="50" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>296</v>
+        <v>154</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>391</v>
+        <v>320</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="L35" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35" s="50">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N35" s="50">
-        <v>40</v>
-      </c>
-      <c r="O35" s="78" t="s">
-        <v>339</v>
+        <v>11</v>
+      </c>
+      <c r="O35" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P35" s="54">
-        <v>2.52E-2</v>
+        <v>0.66449999999999998</v>
       </c>
       <c r="Q35" s="54">
         <f t="shared" si="2"/>
-        <v>1.008</v>
-      </c>
-      <c r="R35" s="52"/>
+        <v>7.3094999999999999</v>
+      </c>
+      <c r="R35" s="64"/>
       <c r="S35" s="52"/>
     </row>
-    <row r="36" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="38">
-        <f>ROW(B36) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="72" t="s">
-        <v>334</v>
+      <c r="C36" s="60" t="s">
+        <v>397</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F36" s="46" t="s">
-        <v>393</v>
-      </c>
-      <c r="G36" s="47" t="s">
-        <v>163</v>
+        <v>311</v>
+      </c>
+      <c r="G36" s="46" t="s">
+        <v>155</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="K36" s="46" t="s">
-        <v>335</v>
+        <v>275</v>
       </c>
       <c r="L36" s="47">
         <v>1</v>
@@ -4276,53 +4164,53 @@
         <v>10</v>
       </c>
       <c r="N36" s="46">
-        <v>20</v>
-      </c>
-      <c r="O36" s="75" t="s">
-        <v>339</v>
+        <v>12</v>
+      </c>
+      <c r="O36" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P36" s="53">
-        <v>4.9000000000000002E-2</v>
+        <v>0.42520000000000002</v>
       </c>
       <c r="Q36" s="53">
         <f t="shared" si="2"/>
-        <v>0.98</v>
-      </c>
-      <c r="R36" s="48"/>
+        <v>5.1024000000000003</v>
+      </c>
+      <c r="R36" s="65"/>
       <c r="S36" s="48"/>
     </row>
-    <row r="37" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="63" t="s">
-        <v>334</v>
+      <c r="C37" s="59" t="s">
+        <v>397</v>
       </c>
       <c r="D37" s="50" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F37" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>217</v>
+        <v>311</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>156</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -4332,53 +4220,53 @@
         <v>10</v>
       </c>
       <c r="N37" s="50">
-        <v>50</v>
-      </c>
-      <c r="O37" s="76" t="s">
-        <v>339</v>
-      </c>
-      <c r="P37" s="77">
-        <v>1.95E-2</v>
+        <v>12</v>
+      </c>
+      <c r="O37" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="P37" s="54">
+        <v>0.16500000000000001</v>
       </c>
       <c r="Q37" s="54">
         <f t="shared" si="2"/>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="R37" s="52"/>
+        <v>1.98</v>
+      </c>
+      <c r="R37" s="64"/>
       <c r="S37" s="52"/>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="38">
-        <f>ROW(B38) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="72" t="s">
-        <v>424</v>
+      <c r="C38" s="60" t="s">
+        <v>397</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="G38" s="47" t="s">
-        <v>165</v>
+        <v>157</v>
+      </c>
+      <c r="G38" s="46" t="s">
+        <v>386</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>255</v>
+        <v>387</v>
       </c>
       <c r="I38" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J38" s="46" t="s">
-        <v>341</v>
+        <v>388</v>
       </c>
       <c r="K38" s="46" t="s">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="L38" s="47">
         <v>1</v>
@@ -4388,107 +4276,109 @@
         <v>10</v>
       </c>
       <c r="N38" s="46">
-        <v>15</v>
-      </c>
-      <c r="O38" s="75" t="s">
-        <v>339</v>
+        <v>50</v>
+      </c>
+      <c r="O38" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P38" s="53">
-        <v>8.7499999999999994E-2</v>
+        <v>9.7000000000000003E-3</v>
       </c>
       <c r="Q38" s="53">
         <f t="shared" si="2"/>
-        <v>1.3125</v>
-      </c>
-      <c r="R38" s="48"/>
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="R38" s="65"/>
       <c r="S38" s="48"/>
     </row>
     <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="63" t="s">
-        <v>425</v>
+      <c r="C39" s="59" t="s">
+        <v>397</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="G39" s="82" t="s">
-        <v>218</v>
+        <v>311</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>158</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="I39" s="50"/>
+        <v>238</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>313</v>
+      </c>
       <c r="J39" s="50" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>335</v>
+        <v>278</v>
       </c>
       <c r="L39" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N39" s="50">
-        <v>20</v>
-      </c>
-      <c r="O39" s="78" t="s">
-        <v>339</v>
+        <v>30</v>
+      </c>
+      <c r="O39" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P39" s="54">
-        <v>2.5600000000000001E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="Q39" s="54">
         <f t="shared" si="2"/>
-        <v>0.51200000000000001</v>
-      </c>
-      <c r="R39" s="52"/>
+        <v>1.9350000000000001</v>
+      </c>
+      <c r="R39" s="64"/>
       <c r="S39" s="52"/>
     </row>
-    <row r="40" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="38">
-        <f>ROW(B40) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="72" t="s">
-        <v>424</v>
+      <c r="C40" s="60" t="s">
+        <v>397</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>333</v>
+        <v>157</v>
       </c>
       <c r="G40" s="46" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="I40" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K40" s="46" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="L40" s="47">
         <v>1</v>
@@ -4498,53 +4388,53 @@
         <v>10</v>
       </c>
       <c r="N40" s="46">
-        <v>12</v>
-      </c>
-      <c r="O40" s="79" t="s">
-        <v>339</v>
-      </c>
-      <c r="P40" s="80">
-        <v>0.66449999999999998</v>
+        <v>20</v>
+      </c>
+      <c r="O40" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="P40" s="53">
+        <v>8.5900000000000004E-2</v>
       </c>
       <c r="Q40" s="53">
         <f t="shared" si="2"/>
-        <v>7.9740000000000002</v>
-      </c>
-      <c r="R40" s="48"/>
+        <v>1.718</v>
+      </c>
+      <c r="R40" s="65"/>
       <c r="S40" s="48"/>
     </row>
-    <row r="41" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="63" t="s">
-        <v>426</v>
+      <c r="C41" s="59" t="s">
+        <v>397</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>333</v>
-      </c>
-      <c r="G41" s="51" t="s">
-        <v>168</v>
+        <v>157</v>
+      </c>
+      <c r="G41" s="50" t="s">
+        <v>201</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J41" s="50" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -4554,433 +4444,440 @@
         <v>10</v>
       </c>
       <c r="N41" s="50">
-        <v>12</v>
-      </c>
-      <c r="O41" s="78" t="s">
-        <v>339</v>
+        <v>50</v>
+      </c>
+      <c r="O41" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P41" s="54">
-        <v>0.42520000000000002</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="Q41" s="54">
         <f t="shared" si="2"/>
-        <v>5.1024000000000003</v>
-      </c>
-      <c r="R41" s="52"/>
+        <v>0.48</v>
+      </c>
+      <c r="R41" s="64"/>
       <c r="S41" s="52"/>
     </row>
-    <row r="42" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="38">
-        <f>ROW(B42) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="72" t="s">
-        <v>426</v>
-      </c>
-      <c r="D42" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="F42" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="G42" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="H42" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46" t="s">
-        <v>364</v>
-      </c>
-      <c r="K42" s="46" t="s">
-        <v>298</v>
-      </c>
-      <c r="L42" s="47">
-        <v>1</v>
-      </c>
-      <c r="M42" s="46">
+      <c r="C42" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="D42" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="84" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="83" t="s">
+        <v>311</v>
+      </c>
+      <c r="G42" s="83" t="s">
+        <v>159</v>
+      </c>
+      <c r="H42" s="83" t="s">
+        <v>241</v>
+      </c>
+      <c r="I42" s="83"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83" t="s">
+        <v>313</v>
+      </c>
+      <c r="L42" s="84">
+        <v>4</v>
+      </c>
+      <c r="M42" s="83">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N42" s="46">
-        <v>12</v>
-      </c>
-      <c r="O42" s="75" t="s">
-        <v>339</v>
-      </c>
-      <c r="P42" s="53">
-        <v>0.22</v>
-      </c>
-      <c r="Q42" s="53">
+        <v>40</v>
+      </c>
+      <c r="N42" s="83"/>
+      <c r="O42" s="85"/>
+      <c r="P42" s="86"/>
+      <c r="Q42" s="86">
         <f t="shared" si="2"/>
-        <v>2.64</v>
-      </c>
-      <c r="R42" s="48"/>
-      <c r="S42" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="65" t="s">
+        <v>414</v>
+      </c>
+      <c r="S42" s="87"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="63" t="s">
-        <v>426</v>
+      <c r="C43" s="59" t="s">
+        <v>396</v>
       </c>
       <c r="D43" s="50" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="G43" s="51" t="s">
-        <v>415</v>
+        <v>160</v>
+      </c>
+      <c r="G43" s="80">
+        <v>61300211121</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>416</v>
+        <v>242</v>
       </c>
       <c r="I43" s="50" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="J43" s="50" t="s">
-        <v>417</v>
+        <v>369</v>
       </c>
       <c r="K43" s="50" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="L43" s="51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M43" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="N43" s="50">
         <v>50</v>
       </c>
-      <c r="O43" s="78" t="s">
-        <v>339</v>
+      <c r="O43" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P43" s="54">
-        <v>9.7000000000000003E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="Q43" s="54">
         <f t="shared" si="2"/>
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="R43" s="52"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="R43" s="64"/>
       <c r="S43" s="52"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="38">
-        <f>ROW(B44) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="72" t="s">
-        <v>426</v>
+      <c r="C44" s="60" t="s">
+        <v>396</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="G44" s="47" t="s">
-        <v>171</v>
+        <v>161</v>
+      </c>
+      <c r="G44" s="81">
+        <v>61300611121</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="I44" s="46" t="s">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="J44" s="46" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="K44" s="46" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="L44" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="46">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N44" s="46">
         <v>20</v>
       </c>
-      <c r="N44" s="46">
-        <v>30</v>
-      </c>
-      <c r="O44" s="75" t="s">
-        <v>339</v>
+      <c r="O44" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P44" s="53">
-        <v>6.5100000000000005E-2</v>
+        <v>3.15E-2</v>
       </c>
       <c r="Q44" s="53">
         <f t="shared" si="2"/>
-        <v>1.9530000000000001</v>
-      </c>
-      <c r="R44" s="48"/>
+        <v>0.63</v>
+      </c>
+      <c r="R44" s="65"/>
       <c r="S44" s="48"/>
     </row>
-    <row r="45" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="63" t="s">
-        <v>426</v>
+      <c r="C45" s="59" t="s">
+        <v>399</v>
       </c>
       <c r="D45" s="50" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="G45" s="51" t="s">
-        <v>219</v>
+        <v>162</v>
+      </c>
+      <c r="G45" s="50" t="s">
+        <v>313</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="I45" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J45" s="50" t="s">
-        <v>366</v>
+        <v>313</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="L45" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M45" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N45" s="50">
-        <v>20</v>
-      </c>
-      <c r="O45" s="78" t="s">
-        <v>339</v>
-      </c>
-      <c r="P45" s="54">
-        <v>8.5900000000000004E-2</v>
-      </c>
-      <c r="Q45" s="54">
-        <f t="shared" si="2"/>
-        <v>1.718</v>
-      </c>
-      <c r="R45" s="52"/>
-      <c r="S45" s="52"/>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="N45" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="O45" s="63" t="s">
+        <v>313</v>
+      </c>
+      <c r="P45" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q45" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="R45" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="S45" s="52" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="38">
-        <f>ROW(B46) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="72" t="s">
-        <v>426</v>
+      <c r="C46" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F46" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="G46" s="47" t="s">
-        <v>220</v>
+        <v>163</v>
+      </c>
+      <c r="G46" s="46" t="s">
+        <v>202</v>
       </c>
       <c r="H46" s="46" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="I46" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J46" s="46" t="s">
-        <v>367</v>
+        <v>321</v>
       </c>
       <c r="K46" s="46" t="s">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="L46" s="47">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M46" s="46">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="N46" s="46">
-        <v>50</v>
-      </c>
-      <c r="O46" s="75" t="s">
-        <v>339</v>
+        <v>200</v>
+      </c>
+      <c r="O46" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P46" s="53">
-        <v>9.5999999999999992E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q46" s="53">
         <f t="shared" si="2"/>
-        <v>0.48</v>
-      </c>
-      <c r="R46" s="48"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R46" s="65"/>
       <c r="S46" s="48"/>
     </row>
-    <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="102" t="s">
-        <v>427</v>
+      <c r="C47" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D47" s="50" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>333</v>
-      </c>
-      <c r="G47" s="51" t="s">
-        <v>172</v>
+        <v>163</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>367</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>262</v>
-      </c>
-      <c r="I47" s="50"/>
-      <c r="J47" s="50"/>
+        <v>243</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="J47" s="50" t="s">
+        <v>372</v>
+      </c>
       <c r="K47" s="50" t="s">
-        <v>335</v>
+        <v>281</v>
       </c>
       <c r="L47" s="51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M47" s="50">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="54"/>
+        <v>10</v>
+      </c>
+      <c r="N47" s="50">
+        <v>50</v>
+      </c>
+      <c r="O47" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="P47" s="54">
+        <v>4.1000000000000003E-3</v>
+      </c>
       <c r="Q47" s="54">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R47" s="52"/>
+        <v>0.20500000000000002</v>
+      </c>
+      <c r="R47" s="64"/>
       <c r="S47" s="52"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="38">
-        <f>ROW(B48) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="72" t="s">
-        <v>425</v>
+      <c r="C48" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="G48" s="81">
-        <v>61300211121</v>
+        <v>163</v>
+      </c>
+      <c r="G48" s="46" t="s">
+        <v>203</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="I48" s="84" t="s">
-        <v>395</v>
-      </c>
-      <c r="J48" s="84" t="s">
-        <v>396</v>
+        <v>222</v>
+      </c>
+      <c r="I48" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J48" s="46" t="s">
+        <v>343</v>
       </c>
       <c r="K48" s="46" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="L48" s="47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M48" s="46">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N48" s="46">
-        <v>50</v>
-      </c>
-      <c r="O48" s="79" t="s">
-        <v>339</v>
-      </c>
-      <c r="P48" s="80">
-        <v>1.3599999999999999E-2</v>
+        <v>100</v>
+      </c>
+      <c r="O48" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="P48" s="53">
+        <v>1.4E-3</v>
       </c>
       <c r="Q48" s="53">
         <f t="shared" si="2"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="R48" s="48"/>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R48" s="65"/>
       <c r="S48" s="48"/>
     </row>
     <row r="49" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="63" t="s">
-        <v>425</v>
+      <c r="C49" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D49" s="50" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="G49" s="82">
-        <v>61300611121</v>
+        <v>163</v>
+      </c>
+      <c r="G49" s="50" t="s">
+        <v>204</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>263</v>
-      </c>
-      <c r="I49" s="83" t="s">
-        <v>397</v>
-      </c>
-      <c r="J49" s="83" t="s">
-        <v>398</v>
+        <v>244</v>
+      </c>
+      <c r="I49" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="J49" s="50" t="s">
+        <v>344</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="L49" s="51">
         <v>1</v>
@@ -4990,168 +4887,165 @@
         <v>10</v>
       </c>
       <c r="N49" s="50">
-        <v>20</v>
-      </c>
-      <c r="O49" s="76" t="s">
-        <v>339</v>
-      </c>
-      <c r="P49" s="77">
-        <v>3.15E-2</v>
+        <v>100</v>
+      </c>
+      <c r="O49" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="P49" s="54">
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="Q49" s="54">
         <f t="shared" si="2"/>
-        <v>0.63</v>
-      </c>
-      <c r="R49" s="52"/>
+        <v>0.22</v>
+      </c>
+      <c r="R49" s="64"/>
       <c r="S49" s="52"/>
     </row>
-    <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="38">
-        <f>ROW(B50) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="72" t="s">
-        <v>428</v>
+      <c r="C50" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D50" s="46" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="G50" s="47" t="s">
-        <v>335</v>
+        <v>164</v>
+      </c>
+      <c r="G50" s="46" t="s">
+        <v>373</v>
       </c>
       <c r="H50" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="I50" s="47" t="s">
-        <v>335</v>
+        <v>245</v>
+      </c>
+      <c r="I50" s="46" t="s">
+        <v>313</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="K50" s="46" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
       <c r="L50" s="47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M50" s="46">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N50" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="O50" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="P50" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q50" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="R50" s="47" t="s">
-        <v>335</v>
-      </c>
-      <c r="S50" s="46" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="N50" s="46">
+        <v>20</v>
+      </c>
+      <c r="O50" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="P50" s="53">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="Q50" s="53">
+        <f t="shared" si="2"/>
+        <v>0.51</v>
+      </c>
+      <c r="R50" s="65"/>
+      <c r="S50" s="48"/>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="63" t="s">
-        <v>429</v>
+      <c r="C51" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D51" s="50" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>221</v>
+        <v>163</v>
+      </c>
+      <c r="G51" s="50" t="s">
+        <v>205</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J51" s="50" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="L51" s="51">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M51" s="50">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="N51" s="50">
-        <v>200</v>
-      </c>
-      <c r="O51" s="76" t="s">
-        <v>339</v>
-      </c>
-      <c r="P51" s="77">
-        <v>1.6999999999999999E-3</v>
+        <v>100</v>
+      </c>
+      <c r="O51" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="P51" s="54">
+        <v>1.5E-3</v>
       </c>
       <c r="Q51" s="54">
         <f t="shared" si="2"/>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="R51" s="52"/>
+        <v>0.15</v>
+      </c>
+      <c r="R51" s="64"/>
       <c r="S51" s="52"/>
     </row>
-    <row r="52" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="38">
-        <f>ROW(B52) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C52" s="72" t="s">
-        <v>429</v>
+      <c r="C52" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D52" s="46" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G52" s="47" t="s">
-        <v>394</v>
+        <v>164</v>
+      </c>
+      <c r="G52" s="46" t="s">
+        <v>206</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="I52" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J52" s="46" t="s">
-        <v>399</v>
+        <v>346</v>
       </c>
       <c r="K52" s="46" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="L52" s="47">
         <v>1</v>
@@ -5161,165 +5055,165 @@
         <v>10</v>
       </c>
       <c r="N52" s="46">
-        <v>50</v>
-      </c>
-      <c r="O52" s="75" t="s">
-        <v>339</v>
+        <v>20</v>
+      </c>
+      <c r="O52" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P52" s="53">
-        <v>4.1000000000000003E-3</v>
+        <v>3.7600000000000001E-2</v>
       </c>
       <c r="Q52" s="53">
         <f t="shared" si="2"/>
-        <v>0.20500000000000002</v>
-      </c>
-      <c r="R52" s="48"/>
+        <v>0.752</v>
+      </c>
+      <c r="R52" s="65"/>
       <c r="S52" s="48"/>
     </row>
-    <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B53) - ROW($B$9)</f>
         <v>44</v>
       </c>
-      <c r="C53" s="63" t="s">
-        <v>429</v>
+      <c r="C53" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D53" s="50" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G53" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="G53" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="H53" s="50" t="s">
         <v>222</v>
       </c>
-      <c r="H53" s="50" t="s">
-        <v>242</v>
-      </c>
       <c r="I53" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J53" s="50" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="L53" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" s="50">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N53" s="50">
         <v>100</v>
       </c>
-      <c r="O53" s="78" t="s">
-        <v>339</v>
+      <c r="O53" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P53" s="54">
-        <v>1.4E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="Q53" s="54">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R53" s="52"/>
+        <v>0.18</v>
+      </c>
+      <c r="R53" s="64"/>
       <c r="S53" s="52"/>
     </row>
     <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="38">
-        <f>ROW(B54) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="72" t="s">
-        <v>429</v>
+      <c r="C54" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D54" s="46" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F54" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G54" s="47" t="s">
-        <v>223</v>
+        <v>163</v>
+      </c>
+      <c r="G54" s="46" t="s">
+        <v>208</v>
       </c>
       <c r="H54" s="46" t="s">
-        <v>265</v>
+        <v>222</v>
       </c>
       <c r="I54" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J54" s="46" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="K54" s="46" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="L54" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54" s="46">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N54" s="46">
         <v>100</v>
       </c>
-      <c r="O54" s="75" t="s">
-        <v>339</v>
+      <c r="O54" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P54" s="53">
-        <v>2.2000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q54" s="53">
         <f t="shared" si="2"/>
-        <v>0.22</v>
-      </c>
-      <c r="R54" s="48"/>
+        <v>0.13</v>
+      </c>
+      <c r="R54" s="65"/>
       <c r="S54" s="48"/>
     </row>
-    <row r="55" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
-      <c r="C55" s="63" t="s">
-        <v>429</v>
+      <c r="C55" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D55" s="50" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="G55" s="51" t="s">
-        <v>400</v>
+        <v>163</v>
+      </c>
+      <c r="G55" s="50" t="s">
+        <v>209</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J55" s="50" t="s">
-        <v>401</v>
+        <v>349</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="L55" s="51">
         <v>1</v>
@@ -5329,53 +5223,53 @@
         <v>10</v>
       </c>
       <c r="N55" s="50">
-        <v>20</v>
-      </c>
-      <c r="O55" s="78" t="s">
-        <v>339</v>
+        <v>100</v>
+      </c>
+      <c r="O55" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P55" s="54">
-        <v>2.8899999999999999E-2</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q55" s="54">
         <f t="shared" si="2"/>
-        <v>0.57799999999999996</v>
-      </c>
-      <c r="R55" s="52"/>
+        <v>0.13</v>
+      </c>
+      <c r="R55" s="64"/>
       <c r="S55" s="52"/>
     </row>
     <row r="56" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="38">
-        <f>ROW(B56) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="72" t="s">
-        <v>429</v>
+      <c r="C56" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D56" s="46" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G56" s="47" t="s">
-        <v>224</v>
+        <v>163</v>
+      </c>
+      <c r="G56" s="46" t="s">
+        <v>375</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I56" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J56" s="46" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="K56" s="46" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="L56" s="47">
         <v>1</v>
@@ -5387,163 +5281,161 @@
       <c r="N56" s="46">
         <v>100</v>
       </c>
-      <c r="O56" s="75" t="s">
-        <v>339</v>
+      <c r="O56" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P56" s="53">
-        <v>1.5E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q56" s="53">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="R56" s="48"/>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R56" s="65"/>
       <c r="S56" s="48"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
-      <c r="C57" s="63" t="s">
-        <v>429</v>
+      <c r="C57" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D57" s="50" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="G57" s="51" t="s">
-        <v>225</v>
+        <v>163</v>
+      </c>
+      <c r="G57" s="50" t="s">
+        <v>210</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I57" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J57" s="50" t="s">
-        <v>371</v>
+        <v>322</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="L57" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N57" s="50">
-        <v>20</v>
-      </c>
-      <c r="O57" s="78" t="s">
-        <v>339</v>
+        <v>40</v>
+      </c>
+      <c r="O57" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P57" s="54">
-        <v>4.1700000000000001E-2</v>
+        <v>3.2899999999999999E-2</v>
       </c>
       <c r="Q57" s="54">
         <f t="shared" si="2"/>
-        <v>0.83400000000000007</v>
-      </c>
-      <c r="R57" s="52"/>
+        <v>1.3159999999999998</v>
+      </c>
+      <c r="R57" s="64"/>
       <c r="S57" s="52"/>
     </row>
-    <row r="58" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="38">
-        <f>ROW(B58) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="72" t="s">
-        <v>429</v>
+      <c r="C58" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E58" s="47" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G58" s="47" t="s">
-        <v>226</v>
+        <v>163</v>
+      </c>
+      <c r="G58" s="81" t="s">
+        <v>211</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I58" s="46" t="s">
-        <v>335</v>
+        <v>389</v>
       </c>
       <c r="J58" s="46" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="K58" s="46" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="L58" s="47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M58" s="46">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="N58" s="46">
-        <v>100</v>
-      </c>
-      <c r="O58" s="75" t="s">
-        <v>339</v>
+        <v>50</v>
+      </c>
+      <c r="O58" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P58" s="53">
-        <v>1.8E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="2"/>
-        <v>0.18</v>
-      </c>
-      <c r="R58" s="48"/>
+        <v>0.36</v>
+      </c>
+      <c r="R58" s="65"/>
       <c r="S58" s="48"/>
     </row>
-    <row r="59" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="63" t="s">
-        <v>429</v>
+      <c r="C59" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D59" s="50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G59" s="51" t="s">
-        <v>227</v>
+        <v>163</v>
+      </c>
+      <c r="G59" s="50" t="s">
+        <v>212</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="I59" s="50" t="s">
-        <v>335</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="I59" s="50"/>
       <c r="J59" s="50" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="L59" s="51">
         <v>2</v>
@@ -5553,53 +5445,53 @@
         <v>20</v>
       </c>
       <c r="N59" s="50">
-        <v>100</v>
-      </c>
-      <c r="O59" s="78" t="s">
-        <v>339</v>
+        <v>40</v>
+      </c>
+      <c r="O59" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P59" s="54">
-        <v>1.2999999999999999E-3</v>
+        <v>3.5499999999999997E-2</v>
       </c>
       <c r="Q59" s="54">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="R59" s="52"/>
+        <v>1.42</v>
+      </c>
+      <c r="R59" s="64"/>
       <c r="S59" s="52"/>
     </row>
-    <row r="60" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="38">
-        <f>ROW(B60) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="72" t="s">
-        <v>429</v>
+      <c r="C60" s="60" t="s">
+        <v>400</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G60" s="47" t="s">
-        <v>228</v>
+        <v>165</v>
+      </c>
+      <c r="G60" s="46" t="s">
+        <v>213</v>
       </c>
       <c r="H60" s="46" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J60" s="46" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="K60" s="46" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="L60" s="47">
         <v>1</v>
@@ -5609,19 +5501,19 @@
         <v>10</v>
       </c>
       <c r="N60" s="46">
-        <v>100</v>
-      </c>
-      <c r="O60" s="75" t="s">
-        <v>339</v>
+        <v>20</v>
+      </c>
+      <c r="O60" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P60" s="53">
-        <v>1.2999999999999999E-3</v>
+        <v>3.9100000000000003E-2</v>
       </c>
       <c r="Q60" s="53">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="R60" s="48"/>
+        <v>0.78200000000000003</v>
+      </c>
+      <c r="R60" s="65"/>
       <c r="S60" s="48"/>
     </row>
     <row r="61" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5630,32 +5522,30 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="63" t="s">
-        <v>429</v>
+      <c r="C61" s="59" t="s">
+        <v>400</v>
       </c>
       <c r="D61" s="50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>402</v>
+        <v>163</v>
+      </c>
+      <c r="G61" s="50" t="s">
+        <v>214</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="I61" s="50" t="s">
-        <v>335</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="I61" s="50"/>
       <c r="J61" s="50" t="s">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="L61" s="51">
         <v>1</v>
@@ -5665,19 +5555,19 @@
         <v>10</v>
       </c>
       <c r="N61" s="50">
-        <v>100</v>
-      </c>
-      <c r="O61" s="78" t="s">
-        <v>339</v>
+        <v>50</v>
+      </c>
+      <c r="O61" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P61" s="54">
-        <v>1.4E-3</v>
+        <v>1.43E-2</v>
       </c>
       <c r="Q61" s="54">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R61" s="52"/>
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="R61" s="64"/>
       <c r="S61" s="52"/>
     </row>
     <row r="62" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5686,164 +5576,167 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="95" t="s">
-        <v>429</v>
-      </c>
-      <c r="D62" s="96" t="s">
-        <v>59</v>
-      </c>
-      <c r="E62" s="97" t="s">
-        <v>132</v>
-      </c>
-      <c r="F62" s="96" t="s">
-        <v>176</v>
-      </c>
-      <c r="G62" s="97" t="s">
-        <v>229</v>
-      </c>
-      <c r="H62" s="96" t="s">
-        <v>242</v>
-      </c>
-      <c r="I62" s="96" t="s">
-        <v>335</v>
-      </c>
-      <c r="J62" s="96" t="s">
-        <v>344</v>
-      </c>
-      <c r="K62" s="96" t="s">
-        <v>313</v>
+      <c r="C62" s="60" t="s">
+        <v>400</v>
+      </c>
+      <c r="D62" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="F62" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="G62" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="H62" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="I62" s="46"/>
+      <c r="J62" s="46" t="s">
+        <v>353</v>
+      </c>
+      <c r="K62" s="46" t="s">
+        <v>296</v>
       </c>
       <c r="L62" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" s="46">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N62" s="46">
-        <v>20</v>
-      </c>
-      <c r="O62" s="79" t="s">
-        <v>339</v>
-      </c>
-      <c r="P62" s="80">
-        <v>3.2899999999999999E-2</v>
+        <v>100</v>
+      </c>
+      <c r="O62" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="P62" s="53">
+        <v>1E-3</v>
       </c>
       <c r="Q62" s="53">
         <f t="shared" si="2"/>
-        <v>0.65799999999999992</v>
-      </c>
-      <c r="R62" s="48"/>
+        <v>0.1</v>
+      </c>
+      <c r="R62" s="65"/>
       <c r="S62" s="48"/>
     </row>
-    <row r="63" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="38">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="63" t="s">
-        <v>429</v>
+      <c r="C63" s="59" t="s">
+        <v>166</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E63" s="51" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G63" s="82" t="s">
-        <v>230</v>
+        <v>166</v>
+      </c>
+      <c r="G63" s="50" t="s">
+        <v>313</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="I63" s="50" t="s">
-        <v>418</v>
+        <v>313</v>
       </c>
       <c r="J63" s="50" t="s">
-        <v>419</v>
+        <v>313</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L63" s="51">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M63" s="50">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N63" s="50">
-        <v>50</v>
-      </c>
-      <c r="O63" s="78" t="s">
-        <v>339</v>
-      </c>
-      <c r="P63" s="54">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="Q63" s="54">
-        <f t="shared" si="2"/>
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="R63" s="52"/>
-      <c r="S63" s="52"/>
-    </row>
-    <row r="64" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="N63" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="O63" s="63" t="s">
+        <v>313</v>
+      </c>
+      <c r="P63" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q63" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="R63" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="S63" s="52" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="38">
         <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
-      <c r="C64" s="72" t="s">
-        <v>429</v>
+      <c r="C64" s="60" t="s">
+        <v>401</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F64" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G64" s="47" t="s">
-        <v>231</v>
+        <v>311</v>
+      </c>
+      <c r="G64" s="46" t="s">
+        <v>167</v>
       </c>
       <c r="H64" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="I64" s="46"/>
+        <v>246</v>
+      </c>
+      <c r="I64" s="46" t="s">
+        <v>313</v>
+      </c>
       <c r="J64" s="46" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="K64" s="46" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L64" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64" s="46">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N64" s="46">
         <v>20</v>
       </c>
-      <c r="N64" s="46">
-        <v>40</v>
-      </c>
-      <c r="O64" s="75" t="s">
-        <v>339</v>
+      <c r="O64" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P64" s="53">
-        <v>3.5499999999999997E-2</v>
+        <v>6.1899999999999997E-2</v>
       </c>
       <c r="Q64" s="53">
         <f t="shared" si="2"/>
-        <v>1.42</v>
-      </c>
-      <c r="R64" s="48"/>
+        <v>1.238</v>
+      </c>
+      <c r="R64" s="65"/>
       <c r="S64" s="48"/>
     </row>
     <row r="65" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5852,30 +5745,32 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C65" s="63" t="s">
-        <v>429</v>
+      <c r="C65" s="59" t="s">
+        <v>402</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="G65" s="51" t="s">
-        <v>232</v>
+        <v>168</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>216</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="I65" s="50"/>
+        <v>247</v>
+      </c>
+      <c r="I65" s="50" t="s">
+        <v>313</v>
+      </c>
       <c r="J65" s="50" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="L65" s="51">
         <v>1</v>
@@ -5885,19 +5780,21 @@
         <v>10</v>
       </c>
       <c r="N65" s="50">
-        <v>20</v>
-      </c>
-      <c r="O65" s="78" t="s">
-        <v>339</v>
+        <v>11</v>
+      </c>
+      <c r="O65" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P65" s="54">
-        <v>3.9100000000000003E-2</v>
+        <v>1.9761</v>
       </c>
       <c r="Q65" s="54">
         <f t="shared" si="2"/>
-        <v>0.78200000000000003</v>
-      </c>
-      <c r="R65" s="52"/>
+        <v>21.737099999999998</v>
+      </c>
+      <c r="R65" s="64" t="s">
+        <v>394</v>
+      </c>
       <c r="S65" s="52"/>
     </row>
     <row r="66" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5906,29 +5803,31 @@
         <f>ROW(B66) - ROW($B$9)</f>
         <v>57</v>
       </c>
-      <c r="C66" s="95" t="s">
-        <v>429</v>
-      </c>
-      <c r="D66" s="96" t="s">
-        <v>63</v>
-      </c>
-      <c r="E66" s="97" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="96" t="s">
-        <v>179</v>
-      </c>
-      <c r="G66" s="97" t="s">
-        <v>233</v>
-      </c>
-      <c r="H66" s="96" t="s">
-        <v>242</v>
-      </c>
-      <c r="I66" s="96"/>
-      <c r="J66" s="96" t="s">
+      <c r="C66" s="60" t="s">
+        <v>402</v>
+      </c>
+      <c r="D66" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="F66" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="G66" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="H66" s="46" t="s">
+        <v>248</v>
+      </c>
+      <c r="I66" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J66" s="46" t="s">
         <v>377</v>
       </c>
-      <c r="K66" s="96" t="s">
+      <c r="K66" s="46" t="s">
         <v>313</v>
       </c>
       <c r="L66" s="47">
@@ -5939,19 +5838,19 @@
         <v>10</v>
       </c>
       <c r="N66" s="46">
-        <v>20</v>
-      </c>
-      <c r="O66" s="75" t="s">
-        <v>339</v>
+        <v>11</v>
+      </c>
+      <c r="O66" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P66" s="53">
-        <v>4.8300000000000003E-2</v>
+        <v>0.4269</v>
       </c>
       <c r="Q66" s="53">
         <f t="shared" si="2"/>
-        <v>0.96600000000000008</v>
-      </c>
-      <c r="R66" s="48"/>
+        <v>4.6959</v>
+      </c>
+      <c r="R66" s="65"/>
       <c r="S66" s="48"/>
     </row>
     <row r="67" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5960,30 +5859,32 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="63" t="s">
-        <v>429</v>
+      <c r="C67" s="59" t="s">
+        <v>402</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E67" s="51" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G67" s="51" t="s">
-        <v>234</v>
+        <v>391</v>
+      </c>
+      <c r="G67" s="50" t="s">
+        <v>170</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="I67" s="50"/>
+        <v>248</v>
+      </c>
+      <c r="I67" s="50" t="s">
+        <v>313</v>
+      </c>
       <c r="J67" s="50" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="L67" s="51">
         <v>1</v>
@@ -5993,19 +5894,19 @@
         <v>10</v>
       </c>
       <c r="N67" s="50">
-        <v>50</v>
-      </c>
-      <c r="O67" s="78" t="s">
-        <v>339</v>
+        <v>11</v>
+      </c>
+      <c r="O67" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P67" s="54">
-        <v>1.43E-2</v>
+        <v>0.44240000000000002</v>
       </c>
       <c r="Q67" s="54">
         <f t="shared" si="2"/>
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="R67" s="52"/>
+        <v>4.8664000000000005</v>
+      </c>
+      <c r="R67" s="64"/>
       <c r="S67" s="52"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6014,167 +5915,166 @@
         <f>ROW(B68) - ROW($B$9)</f>
         <v>59</v>
       </c>
-      <c r="C68" s="72" t="s">
-        <v>429</v>
+      <c r="C68" s="60" t="s">
+        <v>402</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G68" s="47" t="s">
-        <v>235</v>
+        <v>311</v>
+      </c>
+      <c r="G68" s="46" t="s">
+        <v>171</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="I68" s="46"/>
+        <v>249</v>
+      </c>
+      <c r="I68" s="46" t="s">
+        <v>313</v>
+      </c>
       <c r="J68" s="46" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="K68" s="46" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="L68" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="46">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N68" s="46">
-        <v>100</v>
-      </c>
-      <c r="O68" s="75" t="s">
-        <v>339</v>
+        <v>11</v>
+      </c>
+      <c r="O68" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P68" s="53">
-        <v>1E-3</v>
+        <v>1.6232</v>
       </c>
       <c r="Q68" s="53">
         <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="R68" s="48"/>
+        <v>17.8552</v>
+      </c>
+      <c r="R68" s="65"/>
       <c r="S68" s="48"/>
     </row>
-    <row r="69" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="38">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C69" s="63" t="s">
-        <v>180</v>
+      <c r="C69" s="59" t="s">
+        <v>402</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="G69" s="51" t="s">
-        <v>335</v>
+        <v>168</v>
+      </c>
+      <c r="G69" s="50" t="s">
+        <v>172</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>335</v>
+        <v>250</v>
       </c>
       <c r="I69" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J69" s="50" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="L69" s="51">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M69" s="50">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="N69" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="O69" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="P69" s="54" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q69" s="54" t="s">
-        <v>335</v>
-      </c>
-      <c r="R69" s="52" t="s">
-        <v>335</v>
-      </c>
-      <c r="S69" s="52" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="M69:M77" si="3">L69*10</f>
+        <v>10</v>
+      </c>
+      <c r="N69" s="50">
+        <v>20</v>
+      </c>
+      <c r="O69" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="P69" s="54">
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="Q69" s="54">
+        <f t="shared" ref="Q69:Q77" si="4">P69*N69</f>
+        <v>1.1279999999999999</v>
+      </c>
+      <c r="R69" s="64"/>
+      <c r="S69" s="52"/>
+    </row>
+    <row r="70" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="38">
         <f>ROW(B70) - ROW($B$9)</f>
         <v>61</v>
       </c>
-      <c r="C70" s="72" t="s">
-        <v>430</v>
+      <c r="C70" s="60" t="s">
+        <v>402</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="G70" s="47" t="s">
-        <v>181</v>
+        <v>392</v>
+      </c>
+      <c r="G70" s="46" t="s">
+        <v>173</v>
       </c>
       <c r="H70" s="46" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="I70" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J70" s="46" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="K70" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="L70" s="47">
         <v>1</v>
       </c>
       <c r="M70" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="N70" s="46">
-        <v>20</v>
-      </c>
-      <c r="O70" s="75" t="s">
-        <v>339</v>
+        <v>11</v>
+      </c>
+      <c r="O70" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P70" s="53">
-        <v>5.9499999999999997E-2</v>
+        <v>3.9367000000000001</v>
       </c>
       <c r="Q70" s="53">
-        <f t="shared" si="2"/>
-        <v>1.19</v>
-      </c>
-      <c r="R70" s="48"/>
+        <f t="shared" si="4"/>
+        <v>43.303699999999999</v>
+      </c>
+      <c r="R70" s="65"/>
       <c r="S70" s="48"/>
     </row>
     <row r="71" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6183,56 +6083,54 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="63" t="s">
-        <v>431</v>
+      <c r="C71" s="59" t="s">
+        <v>402</v>
       </c>
       <c r="D71" s="50" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E71" s="51" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="G71" s="51" t="s">
-        <v>236</v>
+        <v>174</v>
+      </c>
+      <c r="G71" s="50" t="s">
+        <v>218</v>
       </c>
       <c r="H71" s="50" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="I71" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J71" s="50" t="s">
-        <v>422</v>
+        <v>359</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="L71" s="51">
         <v>1</v>
       </c>
       <c r="M71" s="50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="N71" s="50">
         <v>11</v>
       </c>
-      <c r="O71" s="78" t="s">
-        <v>339</v>
+      <c r="O71" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P71" s="54">
-        <v>1.9761</v>
+        <v>0.94330000000000003</v>
       </c>
       <c r="Q71" s="54">
-        <f t="shared" si="2"/>
-        <v>21.737099999999998</v>
-      </c>
-      <c r="R71" s="85" t="s">
-        <v>423</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>10.376300000000001</v>
+      </c>
+      <c r="R71" s="64"/>
       <c r="S71" s="52"/>
     </row>
     <row r="72" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6241,256 +6139,240 @@
         <f>ROW(B72) - ROW($B$9)</f>
         <v>63</v>
       </c>
-      <c r="C72" s="72" t="s">
-        <v>431</v>
+      <c r="C72" s="60" t="s">
+        <v>402</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E72" s="47" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>183</v>
-      </c>
-      <c r="G72" s="47" t="s">
-        <v>237</v>
+        <v>175</v>
+      </c>
+      <c r="G72" s="46" t="s">
+        <v>219</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="I72" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J72" s="46" t="s">
-        <v>404</v>
+        <v>360</v>
       </c>
       <c r="K72" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="L72" s="47">
         <v>1</v>
       </c>
       <c r="M72" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="N72" s="46">
         <v>11</v>
       </c>
-      <c r="O72" s="75" t="s">
-        <v>339</v>
+      <c r="O72" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P72" s="53">
-        <v>0.47860000000000003</v>
+        <v>0.72819999999999996</v>
       </c>
       <c r="Q72" s="53">
-        <f t="shared" si="2"/>
-        <v>5.2646000000000006</v>
-      </c>
-      <c r="R72" s="48"/>
+        <f t="shared" si="4"/>
+        <v>8.0101999999999993</v>
+      </c>
+      <c r="R72" s="65"/>
       <c r="S72" s="48"/>
     </row>
-    <row r="73" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="38">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C73" s="63" t="s">
-        <v>431</v>
+      <c r="C73" s="59" t="s">
+        <v>402</v>
       </c>
       <c r="D73" s="50" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>420</v>
-      </c>
-      <c r="G73" s="51" t="s">
-        <v>184</v>
+        <v>176</v>
+      </c>
+      <c r="G73" s="50" t="s">
+        <v>220</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="I73" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J73" s="50" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="L73" s="51">
         <v>1</v>
       </c>
       <c r="M73" s="50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="N73" s="50">
         <v>11</v>
       </c>
-      <c r="O73" s="78" t="s">
-        <v>339</v>
+      <c r="O73" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P73" s="54">
-        <v>0.44240000000000002</v>
+        <v>1.3220000000000001</v>
       </c>
       <c r="Q73" s="54">
-        <f t="shared" si="2"/>
-        <v>4.8664000000000005</v>
-      </c>
-      <c r="R73" s="52"/>
+        <f t="shared" si="4"/>
+        <v>14.542000000000002</v>
+      </c>
+      <c r="R73" s="64"/>
       <c r="S73" s="52"/>
     </row>
-    <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="38">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="72" t="s">
-        <v>431</v>
-      </c>
-      <c r="D74" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="E74" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="F74" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="G74" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="H74" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="I74" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="J74" s="46" t="s">
-        <v>382</v>
-      </c>
-      <c r="K74" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="L74" s="47">
+      <c r="C74" s="82" t="s">
+        <v>402</v>
+      </c>
+      <c r="D74" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="E74" s="84" t="s">
+        <v>137</v>
+      </c>
+      <c r="F74" s="83" t="s">
+        <v>311</v>
+      </c>
+      <c r="G74" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="H74" s="83" t="s">
+        <v>252</v>
+      </c>
+      <c r="I74" s="83"/>
+      <c r="J74" s="83"/>
+      <c r="K74" s="83" t="s">
+        <v>313</v>
+      </c>
+      <c r="L74" s="84">
         <v>1</v>
       </c>
-      <c r="M74" s="46">
-        <f t="shared" si="1"/>
+      <c r="M74" s="83">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N74" s="46">
-        <v>11</v>
-      </c>
-      <c r="O74" s="75" t="s">
-        <v>339</v>
-      </c>
-      <c r="P74" s="53">
-        <v>1.5647</v>
-      </c>
-      <c r="Q74" s="53">
-        <f t="shared" si="2"/>
-        <v>17.2117</v>
-      </c>
-      <c r="R74" s="48"/>
-      <c r="S74" s="48"/>
-    </row>
-    <row r="75" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N74" s="83"/>
+      <c r="O74" s="85"/>
+      <c r="P74" s="86"/>
+      <c r="Q74" s="86">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R74" s="92" t="s">
+        <v>414</v>
+      </c>
+      <c r="S74" s="87"/>
+    </row>
+    <row r="75" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="38">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="63" t="s">
-        <v>431</v>
-      </c>
-      <c r="D75" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E75" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="F75" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="G75" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="H75" s="50" t="s">
-        <v>271</v>
-      </c>
-      <c r="I75" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="J75" s="50" t="s">
-        <v>383</v>
-      </c>
-      <c r="K75" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="L75" s="51">
+      <c r="C75" s="88" t="s">
+        <v>402</v>
+      </c>
+      <c r="D75" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="F75" s="79" t="s">
+        <v>169</v>
+      </c>
+      <c r="G75" s="79">
+        <v>4677</v>
+      </c>
+      <c r="H75" s="79" t="s">
+        <v>253</v>
+      </c>
+      <c r="I75" s="79"/>
+      <c r="J75" s="79"/>
+      <c r="K75" s="79" t="s">
+        <v>313</v>
+      </c>
+      <c r="L75" s="78">
         <v>1</v>
       </c>
-      <c r="M75" s="50">
-        <f t="shared" ref="M75:M83" si="3">L75*10</f>
+      <c r="M75" s="79">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N75" s="50">
-        <v>20</v>
-      </c>
-      <c r="O75" s="78" t="s">
-        <v>339</v>
-      </c>
-      <c r="P75" s="54">
-        <v>5.6399999999999999E-2</v>
-      </c>
-      <c r="Q75" s="54">
-        <f t="shared" ref="Q75:Q83" si="4">P75*N75</f>
-        <v>1.1279999999999999</v>
-      </c>
-      <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
-    </row>
-    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N75" s="79"/>
+      <c r="O75" s="89"/>
+      <c r="P75" s="90"/>
+      <c r="Q75" s="90">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R75" s="93" t="s">
+        <v>414</v>
+      </c>
+      <c r="S75" s="91"/>
+    </row>
+    <row r="76" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="38">
         <f>ROW(B76) - ROW($B$9)</f>
         <v>67</v>
       </c>
-      <c r="C76" s="72" t="s">
-        <v>431</v>
+      <c r="C76" s="60" t="s">
+        <v>403</v>
       </c>
       <c r="D76" s="46" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E76" s="47" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="G76" s="47" t="s">
-        <v>187</v>
+        <v>311</v>
+      </c>
+      <c r="G76" s="46" t="s">
+        <v>178</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="I76" s="46" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="L76" s="47">
         <v>1</v>
@@ -6500,53 +6382,53 @@
         <v>10</v>
       </c>
       <c r="N76" s="46">
-        <v>11</v>
-      </c>
-      <c r="O76" s="75" t="s">
-        <v>339</v>
+        <v>15</v>
+      </c>
+      <c r="O76" s="62" t="s">
+        <v>317</v>
       </c>
       <c r="P76" s="53">
-        <v>3.9367000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="Q76" s="53">
         <f t="shared" si="4"/>
-        <v>43.303699999999999</v>
-      </c>
-      <c r="R76" s="48"/>
+        <v>1.3499999999999999</v>
+      </c>
+      <c r="R76" s="65"/>
       <c r="S76" s="48"/>
     </row>
-    <row r="77" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="38">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="63" t="s">
-        <v>431</v>
+      <c r="C77" s="59" t="s">
+        <v>403</v>
       </c>
       <c r="D77" s="50" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E77" s="51" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>188</v>
-      </c>
-      <c r="G77" s="51" t="s">
-        <v>238</v>
+        <v>311</v>
+      </c>
+      <c r="G77" s="50" t="s">
+        <v>179</v>
       </c>
       <c r="H77" s="50" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="I77" s="50" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="J77" s="50" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>335</v>
+        <v>298</v>
       </c>
       <c r="L77" s="51">
         <v>1</v>
@@ -6556,470 +6438,148 @@
         <v>10</v>
       </c>
       <c r="N77" s="50">
-        <v>11</v>
-      </c>
-      <c r="O77" s="78" t="s">
-        <v>339</v>
+        <v>15</v>
+      </c>
+      <c r="O77" s="63" t="s">
+        <v>317</v>
       </c>
       <c r="P77" s="54">
-        <v>0.94330000000000003</v>
+        <v>6.5100000000000005E-2</v>
       </c>
       <c r="Q77" s="54">
         <f t="shared" si="4"/>
-        <v>10.376300000000001</v>
-      </c>
-      <c r="R77" s="52"/>
+        <v>0.97650000000000003</v>
+      </c>
+      <c r="R77" s="64"/>
       <c r="S77" s="52"/>
     </row>
-    <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
-      <c r="B78" s="38">
-        <f>ROW(B78) - ROW($B$9)</f>
-        <v>69</v>
-      </c>
-      <c r="C78" s="72" t="s">
-        <v>431</v>
-      </c>
-      <c r="D78" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E78" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="F78" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="G78" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="H78" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="I78" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="J78" s="46" t="s">
-        <v>386</v>
-      </c>
-      <c r="K78" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="L78" s="47">
-        <v>1</v>
-      </c>
-      <c r="M78" s="46">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N78" s="46">
-        <v>11</v>
-      </c>
-      <c r="O78" s="75" t="s">
-        <v>339</v>
-      </c>
-      <c r="P78" s="53">
-        <v>0.72819999999999996</v>
-      </c>
-      <c r="Q78" s="53">
-        <f t="shared" si="4"/>
-        <v>8.0101999999999993</v>
-      </c>
-      <c r="R78" s="48"/>
-      <c r="S78" s="48"/>
-    </row>
-    <row r="79" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="33"/>
+      <c r="C78" s="44"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="35"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="37"/>
+      <c r="J78" s="36"/>
+      <c r="K78" s="37"/>
+      <c r="L78" s="37"/>
+      <c r="M78" s="37"/>
+      <c r="N78" s="76" t="s">
+        <v>406</v>
+      </c>
+      <c r="O78" s="77"/>
+      <c r="P78" s="77"/>
+      <c r="Q78" s="66">
+        <f>SUM(Q10:Q77)</f>
+        <v>189.4359</v>
+      </c>
+      <c r="R78" s="72"/>
+      <c r="S78" s="73"/>
+    </row>
+    <row r="79" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
-      <c r="B79" s="38">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="C79" s="63" t="s">
-        <v>431</v>
-      </c>
-      <c r="D79" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="E79" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="F79" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="G79" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="H79" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="I79" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="J79" s="50" t="s">
-        <v>387</v>
-      </c>
-      <c r="K79" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="L79" s="51">
-        <v>1</v>
-      </c>
-      <c r="M79" s="50">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N79" s="50">
-        <v>11</v>
-      </c>
-      <c r="O79" s="78" t="s">
-        <v>339</v>
-      </c>
-      <c r="P79" s="54">
-        <v>1.3220000000000001</v>
-      </c>
-      <c r="Q79" s="54">
-        <f t="shared" si="4"/>
-        <v>14.542000000000002</v>
-      </c>
-      <c r="R79" s="52"/>
-      <c r="S79" s="52"/>
-    </row>
-    <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1"/>
-      <c r="B80" s="38">
-        <f>ROW(B80) - ROW($B$9)</f>
-        <v>71</v>
-      </c>
-      <c r="C80" s="72" t="s">
-        <v>431</v>
-      </c>
-      <c r="D80" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E80" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="F80" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="G80" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="H80" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="L80" s="47">
-        <v>1</v>
-      </c>
-      <c r="M80" s="46">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N80" s="46"/>
-      <c r="O80" s="46"/>
-      <c r="P80" s="53"/>
-      <c r="Q80" s="53">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R80" s="48"/>
-      <c r="S80" s="48"/>
-    </row>
-    <row r="81" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="1"/>
-      <c r="B81" s="38">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="C81" s="63" t="s">
-        <v>431</v>
-      </c>
-      <c r="D81" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="E81" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="F81" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="G81" s="51">
-        <v>4677</v>
-      </c>
-      <c r="H81" s="50" t="s">
-        <v>274</v>
-      </c>
-      <c r="I81" s="50"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="L81" s="51">
-        <v>1</v>
-      </c>
-      <c r="M81" s="50">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N81" s="50"/>
-      <c r="O81" s="50"/>
-      <c r="P81" s="54"/>
-      <c r="Q81" s="54">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R81" s="52"/>
-      <c r="S81" s="52"/>
-    </row>
-    <row r="82" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="1"/>
-      <c r="B82" s="38">
-        <f>ROW(B82) - ROW($B$9)</f>
-        <v>73</v>
-      </c>
-      <c r="C82" s="72" t="s">
-        <v>432</v>
-      </c>
-      <c r="D82" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="E82" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="F82" s="46" t="s">
-        <v>333</v>
-      </c>
-      <c r="G82" s="47" t="s">
-        <v>192</v>
-      </c>
-      <c r="H82" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="I82" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="J82" s="46" t="s">
-        <v>388</v>
-      </c>
-      <c r="K82" s="46" t="s">
-        <v>319</v>
-      </c>
-      <c r="L82" s="47">
-        <v>1</v>
-      </c>
-      <c r="M82" s="46">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N82" s="46">
-        <v>15</v>
-      </c>
-      <c r="O82" s="75" t="s">
-        <v>339</v>
-      </c>
-      <c r="P82" s="53">
-        <v>0.09</v>
-      </c>
-      <c r="Q82" s="53">
-        <f t="shared" si="4"/>
-        <v>1.3499999999999999</v>
-      </c>
-      <c r="R82" s="48"/>
-      <c r="S82" s="48"/>
-    </row>
-    <row r="83" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="B83" s="38">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-      <c r="C83" s="63" t="s">
-        <v>432</v>
-      </c>
-      <c r="D83" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="E83" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="F83" s="50" t="s">
-        <v>333</v>
-      </c>
-      <c r="G83" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="H83" s="50" t="s">
-        <v>276</v>
-      </c>
-      <c r="I83" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="J83" s="50" t="s">
-        <v>389</v>
-      </c>
-      <c r="K83" s="50" t="s">
-        <v>320</v>
-      </c>
-      <c r="L83" s="51">
-        <v>1</v>
-      </c>
-      <c r="M83" s="74">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="N83" s="50">
-        <v>15</v>
-      </c>
-      <c r="O83" s="78" t="s">
-        <v>339</v>
-      </c>
-      <c r="P83" s="54">
-        <v>6.5100000000000005E-2</v>
-      </c>
-      <c r="Q83" s="54">
-        <f t="shared" si="4"/>
-        <v>0.97650000000000003</v>
-      </c>
-      <c r="R83" s="52"/>
-      <c r="S83" s="52"/>
-    </row>
-    <row r="84" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
-      <c r="B84" s="33"/>
-      <c r="C84" s="44"/>
-      <c r="D84" s="34"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="36"/>
-      <c r="G84" s="37"/>
-      <c r="H84" s="36"/>
-      <c r="I84" s="37"/>
-      <c r="J84" s="36"/>
-      <c r="K84" s="37"/>
-      <c r="L84" s="37"/>
-      <c r="M84" s="37"/>
-      <c r="N84" s="98" t="s">
-        <v>435</v>
-      </c>
-      <c r="O84" s="99"/>
-      <c r="P84" s="99"/>
-      <c r="Q84" s="100">
-        <f>SUM(Q10:Q83)</f>
-        <v>192.81560000000002</v>
-      </c>
-      <c r="R84" s="68"/>
-      <c r="S84" s="69"/>
-    </row>
-    <row r="85" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="1"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="45"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="10"/>
-      <c r="N85" s="98" t="s">
-        <v>436</v>
-      </c>
-      <c r="O85" s="99"/>
-      <c r="P85" s="99"/>
-      <c r="Q85" s="101">
-        <f>Q84/10</f>
-        <v>19.281560000000002</v>
-      </c>
-      <c r="R85" s="70"/>
-      <c r="S85" s="71"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="45"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="10"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="76" t="s">
+        <v>407</v>
+      </c>
+      <c r="O79" s="77"/>
+      <c r="P79" s="77"/>
+      <c r="Q79" s="67">
+        <f>Q78/10</f>
+        <v>18.94359</v>
+      </c>
+      <c r="R79" s="74"/>
+      <c r="S79" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R84:S85"/>
-    <mergeCell ref="N84:P84"/>
-    <mergeCell ref="N85:P85"/>
+    <mergeCell ref="R78:S79"/>
+    <mergeCell ref="N78:P78"/>
+    <mergeCell ref="N79:P79"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O20" r:id="rId1" xr:uid="{555D2ED8-9598-4F04-A29C-B2191786B31F}"/>
-    <hyperlink ref="O37" r:id="rId2" xr:uid="{49A618E0-394E-485E-95DE-5840EF2248A1}"/>
-    <hyperlink ref="O40" r:id="rId3" xr:uid="{FCDD50F9-179E-4F4C-9D02-96DDE7B9622D}"/>
-    <hyperlink ref="O38" r:id="rId4" xr:uid="{651A0A39-5CC2-48B9-A83F-14DBF6F4F34C}"/>
-    <hyperlink ref="O51" r:id="rId5" xr:uid="{75081537-5144-40C5-A972-F21F19F0BD3F}"/>
-    <hyperlink ref="O62" r:id="rId6" xr:uid="{A026E52A-497D-45AF-81AF-161036BD67DD}"/>
+    <hyperlink ref="O18" r:id="rId1" xr:uid="{555D2ED8-9598-4F04-A29C-B2191786B31F}"/>
+    <hyperlink ref="O32" r:id="rId2" xr:uid="{49A618E0-394E-485E-95DE-5840EF2248A1}"/>
+    <hyperlink ref="O35" r:id="rId3" xr:uid="{FCDD50F9-179E-4F4C-9D02-96DDE7B9622D}"/>
+    <hyperlink ref="O33" r:id="rId4" xr:uid="{651A0A39-5CC2-48B9-A83F-14DBF6F4F34C}"/>
+    <hyperlink ref="O46" r:id="rId5" xr:uid="{75081537-5144-40C5-A972-F21F19F0BD3F}"/>
+    <hyperlink ref="O57" r:id="rId6" xr:uid="{A026E52A-497D-45AF-81AF-161036BD67DD}"/>
     <hyperlink ref="O10" r:id="rId7" xr:uid="{CE33F638-0650-4075-9D24-9DC0EE24C76E}"/>
     <hyperlink ref="O13" r:id="rId8" xr:uid="{D4E1EC75-7F56-4D22-ADA6-CFE6FFC1872F}"/>
     <hyperlink ref="O14" r:id="rId9" xr:uid="{226D0111-5B69-4FBA-8572-1B5BC54DAFE8}"/>
     <hyperlink ref="O15" r:id="rId10" xr:uid="{285211AF-882C-4DEA-8FA4-BA4D841106DE}"/>
-    <hyperlink ref="O16" r:id="rId11" xr:uid="{C816C815-E700-4A31-B57B-6A2FDF9625F6}"/>
-    <hyperlink ref="O17" r:id="rId12" xr:uid="{5A5A1C0D-5377-41E1-80BE-CBC86979D483}"/>
-    <hyperlink ref="O19" r:id="rId13" xr:uid="{2DE4352B-08D1-4CFA-AFBD-8531C9B58500}"/>
-    <hyperlink ref="O22" r:id="rId14" xr:uid="{B4CDEF8B-CEC7-43A0-A9F6-56EAEEDDBE24}"/>
-    <hyperlink ref="O23" r:id="rId15" xr:uid="{2CEE3725-F70A-451E-A380-7511EA16061C}"/>
-    <hyperlink ref="O24" r:id="rId16" xr:uid="{5862839D-C5EC-4A40-934C-A9C57E4BECC7}"/>
-    <hyperlink ref="O25" r:id="rId17" xr:uid="{7B04A431-944E-4A4A-997B-EC4F1D76DC6B}"/>
-    <hyperlink ref="O26" r:id="rId18" xr:uid="{DA9E30EA-7990-4FA1-A832-0FDE709D02A1}"/>
-    <hyperlink ref="O28" r:id="rId19" xr:uid="{446D6CF7-8D5E-49E6-B678-CAF95E62C263}"/>
-    <hyperlink ref="O29" r:id="rId20" xr:uid="{335E1895-5860-4841-A6ED-952BDA93085A}"/>
-    <hyperlink ref="O30" r:id="rId21" xr:uid="{06D36592-DA49-4ABF-B5C9-1D3B86FE13B5}"/>
-    <hyperlink ref="O31" r:id="rId22" xr:uid="{8F178DE8-2DD2-4D57-BE91-D1E745FFEB73}"/>
-    <hyperlink ref="O34" r:id="rId23" xr:uid="{717565F5-1F14-4CCD-AFF6-B0C21A593AFF}"/>
-    <hyperlink ref="O35" r:id="rId24" xr:uid="{9FFDFF22-06D8-4ED4-8A9B-DFB2463CDC89}"/>
-    <hyperlink ref="O36" r:id="rId25" xr:uid="{16D6D382-09C3-4775-AAAA-FC0295F78BB3}"/>
-    <hyperlink ref="O41" r:id="rId26" xr:uid="{E5E4CFE6-BE6E-478D-A1CF-E49BA204E382}"/>
-    <hyperlink ref="O42" r:id="rId27" xr:uid="{6E6C19CB-15D1-44AB-9917-75FCAAE2FD24}"/>
-    <hyperlink ref="O44" r:id="rId28" xr:uid="{29B7F5E8-2DFF-44D7-B091-DCEFE06E7C83}"/>
-    <hyperlink ref="O45" r:id="rId29" xr:uid="{E0C9FF27-6C36-4E03-AD5E-39435BA180EA}"/>
-    <hyperlink ref="O46" r:id="rId30" xr:uid="{4312D63B-0298-4960-B515-771D3E8B85CC}"/>
-    <hyperlink ref="O48" r:id="rId31" xr:uid="{CF9E712A-1F1E-4155-8BD6-0FC723B65B14}"/>
-    <hyperlink ref="O49" r:id="rId32" xr:uid="{7821C627-2282-46BB-93D0-B1552EBB9F32}"/>
-    <hyperlink ref="O52" r:id="rId33" xr:uid="{6B13A082-931D-4827-A6EA-6926CBA6F3BC}"/>
-    <hyperlink ref="O53" r:id="rId34" xr:uid="{C9F96F3A-83DA-4020-A58D-B9C104DC2244}"/>
-    <hyperlink ref="O54" r:id="rId35" xr:uid="{FA5D3023-C28E-4920-B034-33DE5733A921}"/>
-    <hyperlink ref="O55" r:id="rId36" xr:uid="{45A28338-E148-40B1-8F40-9F443D5C5ECA}"/>
-    <hyperlink ref="O56" r:id="rId37" xr:uid="{80DE6F5E-FB37-4FEA-9AB6-9CF3D331F4C1}"/>
-    <hyperlink ref="O57" r:id="rId38" xr:uid="{442E387C-4D86-402D-BF2B-D77E70F21A89}"/>
-    <hyperlink ref="O58" r:id="rId39" xr:uid="{7A6416FE-6364-440A-8274-C7D7C254C268}"/>
-    <hyperlink ref="O59" r:id="rId40" xr:uid="{41C4DFCD-099A-40C0-92E5-1EC972C0E694}"/>
-    <hyperlink ref="O60" r:id="rId41" xr:uid="{8387B773-ABF8-4F4A-8895-EC0BBF8ED49A}"/>
-    <hyperlink ref="O61" r:id="rId42" xr:uid="{02DA634D-BB35-4D56-A91A-9B93D2A8094A}"/>
-    <hyperlink ref="O64" r:id="rId43" xr:uid="{D95DD3AC-48E1-4E24-9501-32AC06BA6AE4}"/>
-    <hyperlink ref="O65" r:id="rId44" xr:uid="{8734B2D7-3FEB-43C7-99CD-0001A66A385D}"/>
-    <hyperlink ref="O66" r:id="rId45" xr:uid="{689FCB40-8009-4E48-8229-75510456938E}"/>
-    <hyperlink ref="O67" r:id="rId46" xr:uid="{3B8B5D5C-5A16-467A-88FA-616A9AECDA72}"/>
-    <hyperlink ref="O68" r:id="rId47" xr:uid="{5285C8FA-C754-43F5-975E-F2E4D890D95B}"/>
-    <hyperlink ref="O70" r:id="rId48" xr:uid="{316BA8C0-A938-4C50-9743-985F8C76544D}"/>
-    <hyperlink ref="O72" r:id="rId49" xr:uid="{3F8213FD-C01B-4447-91D9-4E057269745D}"/>
-    <hyperlink ref="O73" r:id="rId50" xr:uid="{4B7B4791-27F1-4299-A5B6-C71DB36769D0}"/>
-    <hyperlink ref="O74" r:id="rId51" xr:uid="{B61AFFC2-D62C-447B-B59C-8B33FDC28A19}"/>
-    <hyperlink ref="O75" r:id="rId52" xr:uid="{718AC0C2-915D-4181-ACDC-07D2A1F6A0B7}"/>
-    <hyperlink ref="O76" r:id="rId53" xr:uid="{18D79EB6-DE50-46AB-BB44-09F676D4AA6C}"/>
-    <hyperlink ref="O77" r:id="rId54" xr:uid="{B4F980DB-7127-4AB1-A41E-88F26338262F}"/>
-    <hyperlink ref="O78" r:id="rId55" xr:uid="{3836B695-E401-46D4-A238-E31716D58B39}"/>
-    <hyperlink ref="O79" r:id="rId56" xr:uid="{C5515060-E999-4D3D-B0E1-6DCE2168A002}"/>
-    <hyperlink ref="O83" r:id="rId57" xr:uid="{0C8FCE85-9E44-400B-B214-A57E5DC2AE74}"/>
-    <hyperlink ref="O82" r:id="rId58" xr:uid="{EA4D8B3E-B1C4-476C-A93D-AF10A1C5CEA9}"/>
-    <hyperlink ref="O11" r:id="rId59" xr:uid="{CB961B6A-D153-4513-B95E-8947C1F67452}"/>
-    <hyperlink ref="O12" r:id="rId60" xr:uid="{5DEB9260-0ACF-4732-B3F1-378713AA6CFD}"/>
-    <hyperlink ref="O18" r:id="rId61" xr:uid="{B6BA4ED4-B2FB-4E47-8D3B-9201C9619465}"/>
-    <hyperlink ref="O21" r:id="rId62" xr:uid="{2C744A7C-ED0B-4D7B-A324-CC70807A090B}"/>
-    <hyperlink ref="O27" r:id="rId63" xr:uid="{EAD4CE09-E52D-4C0B-B0B8-638ECD52A411}"/>
-    <hyperlink ref="O32" r:id="rId64" xr:uid="{03F48884-BAD1-4095-AB0D-E2359A0356ED}"/>
-    <hyperlink ref="O33" r:id="rId65" xr:uid="{A0553738-8D52-4CD3-9B03-F88F5C89C901}"/>
-    <hyperlink ref="O39" r:id="rId66" xr:uid="{3B4FD01B-0158-4755-B556-199DD4A4F21C}"/>
-    <hyperlink ref="O43" r:id="rId67" xr:uid="{FBA2F3AF-4786-4158-9B8B-155F2E99379A}"/>
-    <hyperlink ref="O63" r:id="rId68" xr:uid="{014E192F-4F33-4E08-ACE2-4778AE694DE9}"/>
-    <hyperlink ref="O71" r:id="rId69" xr:uid="{EB66FF4B-A503-4BDC-8DEC-B0329A0FF9C7}"/>
+    <hyperlink ref="O17" r:id="rId11" xr:uid="{2DE4352B-08D1-4CFA-AFBD-8531C9B58500}"/>
+    <hyperlink ref="O20" r:id="rId12" xr:uid="{B4CDEF8B-CEC7-43A0-A9F6-56EAEEDDBE24}"/>
+    <hyperlink ref="O21" r:id="rId13" xr:uid="{2CEE3725-F70A-451E-A380-7511EA16061C}"/>
+    <hyperlink ref="O22" r:id="rId14" xr:uid="{5862839D-C5EC-4A40-934C-A9C57E4BECC7}"/>
+    <hyperlink ref="O23" r:id="rId15" xr:uid="{7B04A431-944E-4A4A-997B-EC4F1D76DC6B}"/>
+    <hyperlink ref="O24" r:id="rId16" xr:uid="{DA9E30EA-7990-4FA1-A832-0FDE709D02A1}"/>
+    <hyperlink ref="O26" r:id="rId17" xr:uid="{335E1895-5860-4841-A6ED-952BDA93085A}"/>
+    <hyperlink ref="O27" r:id="rId18" xr:uid="{06D36592-DA49-4ABF-B5C9-1D3B86FE13B5}"/>
+    <hyperlink ref="O28" r:id="rId19" xr:uid="{8F178DE8-2DD2-4D57-BE91-D1E745FFEB73}"/>
+    <hyperlink ref="O30" r:id="rId20" xr:uid="{9FFDFF22-06D8-4ED4-8A9B-DFB2463CDC89}"/>
+    <hyperlink ref="O31" r:id="rId21" xr:uid="{16D6D382-09C3-4775-AAAA-FC0295F78BB3}"/>
+    <hyperlink ref="O36" r:id="rId22" xr:uid="{E5E4CFE6-BE6E-478D-A1CF-E49BA204E382}"/>
+    <hyperlink ref="O37" r:id="rId23" xr:uid="{6E6C19CB-15D1-44AB-9917-75FCAAE2FD24}"/>
+    <hyperlink ref="O39" r:id="rId24" xr:uid="{29B7F5E8-2DFF-44D7-B091-DCEFE06E7C83}"/>
+    <hyperlink ref="O40" r:id="rId25" xr:uid="{E0C9FF27-6C36-4E03-AD5E-39435BA180EA}"/>
+    <hyperlink ref="O41" r:id="rId26" xr:uid="{4312D63B-0298-4960-B515-771D3E8B85CC}"/>
+    <hyperlink ref="O43" r:id="rId27" xr:uid="{CF9E712A-1F1E-4155-8BD6-0FC723B65B14}"/>
+    <hyperlink ref="O44" r:id="rId28" xr:uid="{7821C627-2282-46BB-93D0-B1552EBB9F32}"/>
+    <hyperlink ref="O47" r:id="rId29" xr:uid="{6B13A082-931D-4827-A6EA-6926CBA6F3BC}"/>
+    <hyperlink ref="O48" r:id="rId30" xr:uid="{C9F96F3A-83DA-4020-A58D-B9C104DC2244}"/>
+    <hyperlink ref="O49" r:id="rId31" xr:uid="{FA5D3023-C28E-4920-B034-33DE5733A921}"/>
+    <hyperlink ref="O50" r:id="rId32" xr:uid="{45A28338-E148-40B1-8F40-9F443D5C5ECA}"/>
+    <hyperlink ref="O51" r:id="rId33" xr:uid="{80DE6F5E-FB37-4FEA-9AB6-9CF3D331F4C1}"/>
+    <hyperlink ref="O52" r:id="rId34" xr:uid="{442E387C-4D86-402D-BF2B-D77E70F21A89}"/>
+    <hyperlink ref="O53" r:id="rId35" xr:uid="{7A6416FE-6364-440A-8274-C7D7C254C268}"/>
+    <hyperlink ref="O54" r:id="rId36" xr:uid="{41C4DFCD-099A-40C0-92E5-1EC972C0E694}"/>
+    <hyperlink ref="O55" r:id="rId37" xr:uid="{8387B773-ABF8-4F4A-8895-EC0BBF8ED49A}"/>
+    <hyperlink ref="O56" r:id="rId38" xr:uid="{02DA634D-BB35-4D56-A91A-9B93D2A8094A}"/>
+    <hyperlink ref="O59" r:id="rId39" xr:uid="{D95DD3AC-48E1-4E24-9501-32AC06BA6AE4}"/>
+    <hyperlink ref="O60" r:id="rId40" xr:uid="{8734B2D7-3FEB-43C7-99CD-0001A66A385D}"/>
+    <hyperlink ref="O61" r:id="rId41" xr:uid="{3B8B5D5C-5A16-467A-88FA-616A9AECDA72}"/>
+    <hyperlink ref="O62" r:id="rId42" xr:uid="{5285C8FA-C754-43F5-975E-F2E4D890D95B}"/>
+    <hyperlink ref="O64" r:id="rId43" xr:uid="{316BA8C0-A938-4C50-9743-985F8C76544D}"/>
+    <hyperlink ref="O66" r:id="rId44" xr:uid="{3F8213FD-C01B-4447-91D9-4E057269745D}"/>
+    <hyperlink ref="O67" r:id="rId45" xr:uid="{4B7B4791-27F1-4299-A5B6-C71DB36769D0}"/>
+    <hyperlink ref="O68" r:id="rId46" xr:uid="{B61AFFC2-D62C-447B-B59C-8B33FDC28A19}"/>
+    <hyperlink ref="O69" r:id="rId47" xr:uid="{718AC0C2-915D-4181-ACDC-07D2A1F6A0B7}"/>
+    <hyperlink ref="O70" r:id="rId48" xr:uid="{18D79EB6-DE50-46AB-BB44-09F676D4AA6C}"/>
+    <hyperlink ref="O71" r:id="rId49" xr:uid="{B4F980DB-7127-4AB1-A41E-88F26338262F}"/>
+    <hyperlink ref="O72" r:id="rId50" xr:uid="{3836B695-E401-46D4-A238-E31716D58B39}"/>
+    <hyperlink ref="O73" r:id="rId51" xr:uid="{C5515060-E999-4D3D-B0E1-6DCE2168A002}"/>
+    <hyperlink ref="O77" r:id="rId52" xr:uid="{0C8FCE85-9E44-400B-B214-A57E5DC2AE74}"/>
+    <hyperlink ref="O76" r:id="rId53" xr:uid="{EA4D8B3E-B1C4-476C-A93D-AF10A1C5CEA9}"/>
+    <hyperlink ref="O11" r:id="rId54" xr:uid="{CB961B6A-D153-4513-B95E-8947C1F67452}"/>
+    <hyperlink ref="O12" r:id="rId55" xr:uid="{5DEB9260-0ACF-4732-B3F1-378713AA6CFD}"/>
+    <hyperlink ref="O16" r:id="rId56" xr:uid="{B6BA4ED4-B2FB-4E47-8D3B-9201C9619465}"/>
+    <hyperlink ref="O19" r:id="rId57" xr:uid="{2C744A7C-ED0B-4D7B-A324-CC70807A090B}"/>
+    <hyperlink ref="O29" r:id="rId58" xr:uid="{A0553738-8D52-4CD3-9B03-F88F5C89C901}"/>
+    <hyperlink ref="O34" r:id="rId59" xr:uid="{3B4FD01B-0158-4755-B556-199DD4A4F21C}"/>
+    <hyperlink ref="O38" r:id="rId60" xr:uid="{FBA2F3AF-4786-4158-9B8B-155F2E99379A}"/>
+    <hyperlink ref="O58" r:id="rId61" xr:uid="{014E192F-4F33-4E08-ACE2-4778AE694DE9}"/>
+    <hyperlink ref="O65" r:id="rId62" xr:uid="{EB66FF4B-A503-4BDC-8DEC-B0329A0FF9C7}"/>
+    <hyperlink ref="O25" r:id="rId63" xr:uid="{CFCD8C6D-2653-4D9C-9250-2514B1905C07}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId70"/>
-  <drawing r:id="rId71"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId64"/>
+  <drawing r:id="rId65"/>
 </worksheet>
 </file>
--- a/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
+++ b/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ezlo-VoiceAssistant\Deliverable\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77C85AA-0392-4AE6-B590-8A0DE3D7CFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC6E430-4C6A-49DE-80A5-8331B6928E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="418">
   <si>
     <t>Component list</t>
   </si>
@@ -1274,7 +1274,16 @@
     <t>DZ254R-11-05-63</t>
   </si>
   <si>
-    <t>Need Custom Supplier Quote</t>
+    <t xml:space="preserve">Custom Supplier </t>
+  </si>
+  <si>
+    <t>Karen Quote</t>
+  </si>
+  <si>
+    <t>LY68L6400SLIT</t>
+  </si>
+  <si>
+    <t>C261881</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1295,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1470,14 +1479,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1792,7 +1793,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1977,6 +1978,24 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2009,53 +2028,17 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2415,7 +2398,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" customWidth="1"/>
     <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -2433,15 +2416,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="69"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="75"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2491,7 +2474,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="70"/>
+      <c r="S3" s="76"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2516,7 +2499,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="71"/>
+      <c r="S4" s="77"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2541,7 +2524,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="71"/>
+      <c r="S5" s="77"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2562,7 +2545,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="71"/>
+      <c r="S6" s="77"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2583,7 +2566,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="71"/>
+      <c r="S7" s="77"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2604,7 +2587,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="71"/>
+      <c r="S8" s="77"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3189,7 +3172,7 @@
       <c r="F19" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="G19" s="80" t="s">
+      <c r="G19" s="68" t="s">
         <v>188</v>
       </c>
       <c r="H19" s="50" t="s">
@@ -3525,7 +3508,7 @@
       <c r="F25" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="80" t="s">
+      <c r="G25" s="68" t="s">
         <v>193</v>
       </c>
       <c r="H25" s="50" t="s">
@@ -3749,7 +3732,7 @@
       <c r="F29" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="G29" s="80" t="s">
+      <c r="G29" s="68" t="s">
         <v>197</v>
       </c>
       <c r="H29" s="50" t="s">
@@ -4029,7 +4012,7 @@
       <c r="F34" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="G34" s="81" t="s">
+      <c r="G34" s="69" t="s">
         <v>199</v>
       </c>
       <c r="H34" s="46" t="s">
@@ -4459,53 +4442,63 @@
       <c r="R41" s="64"/>
       <c r="S41" s="52"/>
     </row>
-    <row r="42" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
+    <row r="42" spans="1:19" s="87" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="86"/>
       <c r="B42" s="38">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="82" t="s">
+      <c r="C42" s="60" t="s">
         <v>398</v>
       </c>
-      <c r="D42" s="83" t="s">
+      <c r="D42" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="84" t="s">
+      <c r="E42" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="F42" s="83" t="s">
+      <c r="F42" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="G42" s="83" t="s">
+      <c r="G42" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="83" t="s">
+      <c r="H42" s="46" t="s">
         <v>241</v>
       </c>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83" t="s">
-        <v>313</v>
-      </c>
-      <c r="L42" s="84">
+      <c r="I42" s="84" t="s">
+        <v>313</v>
+      </c>
+      <c r="J42" s="84" t="s">
+        <v>313</v>
+      </c>
+      <c r="K42" s="84" t="s">
+        <v>313</v>
+      </c>
+      <c r="L42" s="85">
         <v>4</v>
       </c>
-      <c r="M42" s="83">
+      <c r="M42" s="46">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N42" s="83"/>
-      <c r="O42" s="85"/>
-      <c r="P42" s="86"/>
-      <c r="Q42" s="86">
+      <c r="N42" s="46">
+        <v>80</v>
+      </c>
+      <c r="O42" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P42" s="53">
+        <v>2.9</v>
+      </c>
+      <c r="Q42" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="R42" s="65" t="s">
-        <v>414</v>
-      </c>
-      <c r="S42" s="87"/>
+        <v>415</v>
+      </c>
+      <c r="S42" s="70"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -4525,7 +4518,7 @@
       <c r="F43" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="G43" s="80">
+      <c r="G43" s="68">
         <v>61300211121</v>
       </c>
       <c r="H43" s="50" t="s">
@@ -4581,7 +4574,7 @@
       <c r="F44" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="81">
+      <c r="G44" s="69">
         <v>61300611121</v>
       </c>
       <c r="H44" s="46" t="s">
@@ -5368,7 +5361,7 @@
       <c r="F58" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="G58" s="81" t="s">
+      <c r="G58" s="69" t="s">
         <v>211</v>
       </c>
       <c r="H58" s="46" t="s">
@@ -6245,101 +6238,119 @@
       <c r="R73" s="64"/>
       <c r="S73" s="52"/>
     </row>
-    <row r="74" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="38">
         <f>ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="82" t="s">
+      <c r="C74" s="60" t="s">
         <v>402</v>
       </c>
-      <c r="D74" s="83" t="s">
+      <c r="D74" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="E74" s="84" t="s">
+      <c r="E74" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="F74" s="83" t="s">
+      <c r="F74" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="G74" s="83" t="s">
+      <c r="G74" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="H74" s="83" t="s">
+      <c r="H74" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="I74" s="83"/>
-      <c r="J74" s="83"/>
-      <c r="K74" s="83" t="s">
-        <v>313</v>
-      </c>
-      <c r="L74" s="84">
+      <c r="I74" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J74" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="K74" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="L74" s="47">
         <v>1</v>
       </c>
-      <c r="M74" s="83">
+      <c r="M74" s="46">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N74" s="83"/>
-      <c r="O74" s="85"/>
-      <c r="P74" s="86"/>
-      <c r="Q74" s="86">
+      <c r="N74" s="46">
+        <v>11</v>
+      </c>
+      <c r="O74" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P74" s="53">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="Q74" s="53">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R74" s="92" t="s">
-        <v>414</v>
-      </c>
-      <c r="S74" s="87"/>
-    </row>
-    <row r="75" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>12.76</v>
+      </c>
+      <c r="R74" s="72" t="s">
+        <v>415</v>
+      </c>
+      <c r="S74" s="70"/>
+    </row>
+    <row r="75" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="38">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="88" t="s">
+      <c r="C75" s="59" t="s">
         <v>402</v>
       </c>
-      <c r="D75" s="79" t="s">
+      <c r="D75" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="E75" s="78" t="s">
+      <c r="E75" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="F75" s="79" t="s">
+      <c r="F75" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="G75" s="79">
+      <c r="G75" s="68">
         <v>4677</v>
       </c>
-      <c r="H75" s="79" t="s">
+      <c r="H75" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="I75" s="79"/>
-      <c r="J75" s="79"/>
-      <c r="K75" s="79" t="s">
-        <v>313</v>
-      </c>
-      <c r="L75" s="78">
+      <c r="I75" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="J75" s="50" t="s">
+        <v>417</v>
+      </c>
+      <c r="K75" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="L75" s="51">
         <v>1</v>
       </c>
-      <c r="M75" s="79">
+      <c r="M75" s="50">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N75" s="79"/>
-      <c r="O75" s="89"/>
-      <c r="P75" s="90"/>
-      <c r="Q75" s="90">
+      <c r="N75" s="50">
+        <v>11</v>
+      </c>
+      <c r="O75" s="63" t="s">
+        <v>414</v>
+      </c>
+      <c r="P75" s="54">
+        <v>2.7662</v>
+      </c>
+      <c r="Q75" s="54">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R75" s="93" t="s">
-        <v>414</v>
-      </c>
-      <c r="S75" s="91"/>
+        <v>30.4282</v>
+      </c>
+      <c r="R75" s="73"/>
+      <c r="S75" s="71"/>
     </row>
     <row r="76" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
@@ -6467,17 +6478,17 @@
       <c r="K78" s="37"/>
       <c r="L78" s="37"/>
       <c r="M78" s="37"/>
-      <c r="N78" s="76" t="s">
+      <c r="N78" s="82" t="s">
         <v>406</v>
       </c>
-      <c r="O78" s="77"/>
-      <c r="P78" s="77"/>
+      <c r="O78" s="83"/>
+      <c r="P78" s="83"/>
       <c r="Q78" s="66">
         <f>SUM(Q10:Q77)</f>
-        <v>189.4359</v>
-      </c>
-      <c r="R78" s="72"/>
-      <c r="S78" s="73"/>
+        <v>464.62409999999994</v>
+      </c>
+      <c r="R78" s="78"/>
+      <c r="S78" s="79"/>
     </row>
     <row r="79" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -6493,17 +6504,17 @@
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
       <c r="M79" s="10"/>
-      <c r="N79" s="76" t="s">
+      <c r="N79" s="82" t="s">
         <v>407</v>
       </c>
-      <c r="O79" s="77"/>
-      <c r="P79" s="77"/>
+      <c r="O79" s="83"/>
+      <c r="P79" s="83"/>
       <c r="Q79" s="67">
         <f>Q78/10</f>
-        <v>18.94359</v>
-      </c>
-      <c r="R79" s="74"/>
-      <c r="S79" s="75"/>
+        <v>46.462409999999991</v>
+      </c>
+      <c r="R79" s="80"/>
+      <c r="S79" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
+++ b/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ezlo-VoiceAssistant\Deliverable\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC6E430-4C6A-49DE-80A5-8331B6928E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DCB7D6-EDDB-4D01-8A3D-C99E7A3DE54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,9 +185,6 @@
     <t>R12</t>
   </si>
   <si>
-    <t>R20</t>
-  </si>
-  <si>
     <t>R23, R24, R25, R26</t>
   </si>
   <si>
@@ -1284,6 +1281,9 @@
   </si>
   <si>
     <t>C261881</t>
+  </si>
+  <si>
+    <t>R20,R30</t>
   </si>
 </sst>
 </file>
@@ -1996,6 +1996,18 @@
     <xf numFmtId="0" fontId="26" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2027,18 +2039,6 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2416,15 +2416,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="75"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="79"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2474,7 +2474,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="76"/>
+      <c r="S3" s="80"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2499,7 +2499,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="77"/>
+      <c r="S4" s="81"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2524,7 +2524,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="77"/>
+      <c r="S5" s="81"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2545,7 +2545,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="77"/>
+      <c r="S6" s="81"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2566,7 +2566,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="77"/>
+      <c r="S7" s="81"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2587,7 +2587,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="77"/>
+      <c r="S8" s="81"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2595,55 +2595,55 @@
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="J9" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="K9" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="K9" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="R9" s="32" t="s">
+      <c r="S9" s="32" t="s">
         <v>308</v>
-      </c>
-      <c r="S9" s="32" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2653,31 +2653,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L10" s="47">
         <v>13</v>
@@ -2690,7 +2690,7 @@
         <v>200</v>
       </c>
       <c r="O10" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P10" s="53">
         <v>2.8999999999999998E-3</v>
@@ -2709,31 +2709,31 @@
         <v>2</v>
       </c>
       <c r="C11" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D11" s="50" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J11" s="50" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L11" s="51">
         <v>4</v>
@@ -2746,7 +2746,7 @@
         <v>50</v>
       </c>
       <c r="O11" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P11" s="54">
         <v>8.8599999999999998E-2</v>
@@ -2756,7 +2756,7 @@
         <v>4.43</v>
       </c>
       <c r="R11" s="64" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S11" s="52"/>
     </row>
@@ -2767,31 +2767,31 @@
         <v>3</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D12" s="46" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L12" s="47">
         <v>2</v>
@@ -2804,7 +2804,7 @@
         <v>22</v>
       </c>
       <c r="O12" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P12" s="53">
         <v>0.48549999999999999</v>
@@ -2814,7 +2814,7 @@
         <v>10.680999999999999</v>
       </c>
       <c r="R12" s="65" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="S12" s="48"/>
     </row>
@@ -2825,31 +2825,31 @@
         <v>4</v>
       </c>
       <c r="C13" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G13" s="50" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P13" s="54">
         <v>2.5000000000000001E-3</v>
@@ -2881,31 +2881,31 @@
         <v>5</v>
       </c>
       <c r="C14" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L14" s="47">
         <v>1</v>
@@ -2918,7 +2918,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P14" s="53">
         <v>3.0999999999999999E-3</v>
@@ -2937,31 +2937,31 @@
         <v>6</v>
       </c>
       <c r="C15" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D15" s="50" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G15" s="50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -2974,7 +2974,7 @@
         <v>40</v>
       </c>
       <c r="O15" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P15" s="54">
         <v>1.4200000000000001E-2</v>
@@ -2993,31 +2993,31 @@
         <v>7</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D16" s="46" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G16" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K16" s="46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L16" s="47">
         <v>2</v>
@@ -3030,7 +3030,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P16" s="53">
         <v>1E-3</v>
@@ -3049,31 +3049,31 @@
         <v>8</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D17" s="50" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G17" s="50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L17" s="51">
         <v>1</v>
@@ -3086,7 +3086,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P17" s="54">
         <v>3.2000000000000002E-3</v>
@@ -3105,31 +3105,31 @@
         <v>9</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D18" s="46" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G18" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L18" s="47">
         <v>1</v>
@@ -3142,7 +3142,7 @@
         <v>20</v>
       </c>
       <c r="O18" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P18" s="53">
         <v>1.7899999999999999E-2</v>
@@ -3161,31 +3161,31 @@
         <v>10</v>
       </c>
       <c r="C19" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D19" s="50" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -3198,7 +3198,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P19" s="54">
         <v>2E-3</v>
@@ -3217,31 +3217,31 @@
         <v>11</v>
       </c>
       <c r="C20" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D20" s="46" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G20" s="46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L20" s="47">
         <v>1</v>
@@ -3254,7 +3254,7 @@
         <v>100</v>
       </c>
       <c r="O20" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P20" s="53">
         <v>2.0999999999999999E-3</v>
@@ -3273,31 +3273,31 @@
         <v>12</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D21" s="50" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G21" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L21" s="51">
         <v>8</v>
@@ -3310,7 +3310,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P21" s="54">
         <v>7.4000000000000003E-3</v>
@@ -3329,31 +3329,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D22" s="46" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K22" s="46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L22" s="47">
         <v>2</v>
@@ -3366,7 +3366,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P22" s="53">
         <v>2.8E-3</v>
@@ -3385,31 +3385,31 @@
         <v>14</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D23" s="50" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G23" s="50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L23" s="51">
         <v>2</v>
@@ -3422,7 +3422,7 @@
         <v>22</v>
       </c>
       <c r="O23" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P23" s="54">
         <v>0.19009999999999999</v>
@@ -3441,31 +3441,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D24" s="46" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G24" s="46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K24" s="46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L24" s="47">
         <v>2</v>
@@ -3478,7 +3478,7 @@
         <v>40</v>
       </c>
       <c r="O24" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P24" s="53">
         <v>2.9000000000000001E-2</v>
@@ -3497,31 +3497,31 @@
         <v>16</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D25" s="50" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G25" s="68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I25" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="J25" s="50" t="s">
         <v>411</v>
       </c>
-      <c r="J25" s="50" t="s">
-        <v>412</v>
-      </c>
       <c r="K25" s="50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L25" s="51">
         <v>2</v>
@@ -3534,7 +3534,7 @@
         <v>50</v>
       </c>
       <c r="O25" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P25" s="54">
         <v>1.1900000000000001E-2</v>
@@ -3553,31 +3553,31 @@
         <v>17</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G26" s="46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K26" s="46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L26" s="47">
         <v>13</v>
@@ -3590,7 +3590,7 @@
         <v>150</v>
       </c>
       <c r="O26" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P26" s="53">
         <v>4.1999999999999997E-3</v>
@@ -3609,31 +3609,31 @@
         <v>18</v>
       </c>
       <c r="C27" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>22</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G27" s="50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -3646,7 +3646,7 @@
         <v>50</v>
       </c>
       <c r="O27" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P27" s="54">
         <v>6.7000000000000002E-3</v>
@@ -3665,31 +3665,31 @@
         <v>19</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D28" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G28" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I28" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K28" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L28" s="47">
         <v>1</v>
@@ -3702,7 +3702,7 @@
         <v>50</v>
       </c>
       <c r="O28" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P28" s="53">
         <v>5.1999999999999998E-3</v>
@@ -3721,31 +3721,31 @@
         <v>20</v>
       </c>
       <c r="C29" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G29" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I29" s="50" t="s">
+        <v>382</v>
+      </c>
+      <c r="J29" s="50" t="s">
         <v>383</v>
       </c>
-      <c r="J29" s="50" t="s">
-        <v>384</v>
-      </c>
       <c r="K29" s="50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L29" s="51">
         <v>6</v>
@@ -3758,7 +3758,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P29" s="54">
         <v>4.4999999999999997E-3</v>
@@ -3777,31 +3777,31 @@
         <v>21</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D30" s="46" t="s">
         <v>24</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G30" s="46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I30" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K30" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L30" s="47">
         <v>2</v>
@@ -3814,7 +3814,7 @@
         <v>40</v>
       </c>
       <c r="O30" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P30" s="53">
         <v>2.52E-2</v>
@@ -3833,31 +3833,31 @@
         <v>22</v>
       </c>
       <c r="C31" s="59" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D31" s="50" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G31" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L31" s="51">
         <v>1</v>
@@ -3870,7 +3870,7 @@
         <v>20</v>
       </c>
       <c r="O31" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P31" s="54">
         <v>4.9000000000000002E-2</v>
@@ -3889,31 +3889,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D32" s="46" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G32" s="46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I32" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J32" s="46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K32" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L32" s="47">
         <v>1</v>
@@ -3926,7 +3926,7 @@
         <v>50</v>
       </c>
       <c r="O32" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P32" s="53">
         <v>1.95E-2</v>
@@ -3945,31 +3945,31 @@
         <v>24</v>
       </c>
       <c r="C33" s="59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D33" s="50" t="s">
         <v>27</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G33" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -3982,7 +3982,7 @@
         <v>15</v>
       </c>
       <c r="O33" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P33" s="54">
         <v>8.7499999999999994E-2</v>
@@ -4001,31 +4001,31 @@
         <v>25</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D34" s="46" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G34" s="69" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I34" s="46" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K34" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L34" s="47">
         <v>1</v>
@@ -4038,7 +4038,7 @@
         <v>20</v>
       </c>
       <c r="O34" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P34" s="53">
         <v>2.5600000000000001E-2</v>
@@ -4057,31 +4057,31 @@
         <v>26</v>
       </c>
       <c r="C35" s="59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D35" s="50" t="s">
         <v>29</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
@@ -4094,7 +4094,7 @@
         <v>11</v>
       </c>
       <c r="O35" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P35" s="54">
         <v>0.66449999999999998</v>
@@ -4113,31 +4113,31 @@
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D36" s="46" t="s">
         <v>30</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F36" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G36" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K36" s="46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L36" s="47">
         <v>1</v>
@@ -4150,7 +4150,7 @@
         <v>12</v>
       </c>
       <c r="O36" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P36" s="53">
         <v>0.42520000000000002</v>
@@ -4169,31 +4169,31 @@
         <v>28</v>
       </c>
       <c r="C37" s="59" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D37" s="50" t="s">
         <v>31</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F37" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G37" s="50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K37" s="50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -4206,7 +4206,7 @@
         <v>12</v>
       </c>
       <c r="O37" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P37" s="54">
         <v>0.16500000000000001</v>
@@ -4225,31 +4225,31 @@
         <v>29</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D38" s="46" t="s">
         <v>32</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G38" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="H38" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="H38" s="46" t="s">
+      <c r="I38" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="J38" s="46" t="s">
         <v>387</v>
       </c>
-      <c r="I38" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="J38" s="46" t="s">
-        <v>388</v>
-      </c>
       <c r="K38" s="46" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L38" s="47">
         <v>1</v>
@@ -4262,7 +4262,7 @@
         <v>50</v>
       </c>
       <c r="O38" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P38" s="53">
         <v>9.7000000000000003E-3</v>
@@ -4281,31 +4281,31 @@
         <v>30</v>
       </c>
       <c r="C39" s="59" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D39" s="50" t="s">
         <v>33</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G39" s="50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J39" s="50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K39" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L39" s="51">
         <v>2</v>
@@ -4318,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="O39" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P39" s="54">
         <v>6.4500000000000002E-2</v>
@@ -4337,31 +4337,31 @@
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D40" s="46" t="s">
         <v>34</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G40" s="46" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I40" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K40" s="46" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L40" s="47">
         <v>1</v>
@@ -4374,7 +4374,7 @@
         <v>20</v>
       </c>
       <c r="O40" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P40" s="53">
         <v>8.5900000000000004E-2</v>
@@ -4393,31 +4393,31 @@
         <v>32</v>
       </c>
       <c r="C41" s="59" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D41" s="50" t="s">
         <v>35</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G41" s="50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J41" s="50" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K41" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -4430,7 +4430,7 @@
         <v>50</v>
       </c>
       <c r="O41" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P41" s="54">
         <v>9.5999999999999992E-3</v>
@@ -4442,40 +4442,40 @@
       <c r="R41" s="64"/>
       <c r="S41" s="52"/>
     </row>
-    <row r="42" spans="1:19" s="87" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="86"/>
+    <row r="42" spans="1:19" s="77" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="76"/>
       <c r="B42" s="38">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D42" s="46" t="s">
         <v>36</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F42" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G42" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="I42" s="84" t="s">
-        <v>313</v>
-      </c>
-      <c r="J42" s="84" t="s">
-        <v>313</v>
-      </c>
-      <c r="K42" s="84" t="s">
-        <v>313</v>
-      </c>
-      <c r="L42" s="85">
+        <v>240</v>
+      </c>
+      <c r="I42" s="74" t="s">
+        <v>312</v>
+      </c>
+      <c r="J42" s="74" t="s">
+        <v>312</v>
+      </c>
+      <c r="K42" s="74" t="s">
+        <v>312</v>
+      </c>
+      <c r="L42" s="75">
         <v>4</v>
       </c>
       <c r="M42" s="46">
@@ -4486,7 +4486,7 @@
         <v>80</v>
       </c>
       <c r="O42" s="62" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P42" s="53">
         <v>2.9</v>
@@ -4496,7 +4496,7 @@
         <v>232</v>
       </c>
       <c r="R42" s="65" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="S42" s="70"/>
     </row>
@@ -4507,31 +4507,31 @@
         <v>34</v>
       </c>
       <c r="C43" s="59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D43" s="50" t="s">
         <v>37</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G43" s="68">
         <v>61300211121</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I43" s="50" t="s">
+        <v>367</v>
+      </c>
+      <c r="J43" s="50" t="s">
         <v>368</v>
       </c>
-      <c r="J43" s="50" t="s">
-        <v>369</v>
-      </c>
       <c r="K43" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L43" s="51">
         <v>4</v>
@@ -4544,7 +4544,7 @@
         <v>50</v>
       </c>
       <c r="O43" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P43" s="54">
         <v>1.4E-2</v>
@@ -4563,31 +4563,31 @@
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D44" s="46" t="s">
         <v>38</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G44" s="69">
         <v>61300611121</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I44" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="J44" s="46" t="s">
         <v>370</v>
       </c>
-      <c r="J44" s="46" t="s">
-        <v>371</v>
-      </c>
       <c r="K44" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L44" s="47">
         <v>1</v>
@@ -4600,7 +4600,7 @@
         <v>20</v>
       </c>
       <c r="O44" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P44" s="53">
         <v>3.15E-2</v>
@@ -4619,31 +4619,31 @@
         <v>36</v>
       </c>
       <c r="C45" s="59" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D45" s="50" t="s">
         <v>39</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G45" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I45" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J45" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K45" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L45" s="51">
         <v>5</v>
@@ -4653,22 +4653,22 @@
         <v>50</v>
       </c>
       <c r="N45" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O45" s="63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P45" s="54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q45" s="54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R45" s="64" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S45" s="52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4678,31 +4678,31 @@
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D46" s="46" t="s">
         <v>40</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F46" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G46" s="46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H46" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I46" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J46" s="46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K46" s="46" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L46" s="47">
         <v>11</v>
@@ -4715,7 +4715,7 @@
         <v>200</v>
       </c>
       <c r="O46" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P46" s="53">
         <v>1.6999999999999999E-3</v>
@@ -4734,31 +4734,31 @@
         <v>38</v>
       </c>
       <c r="C47" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D47" s="50" t="s">
         <v>41</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G47" s="50" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I47" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J47" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K47" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
@@ -4771,7 +4771,7 @@
         <v>50</v>
       </c>
       <c r="O47" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P47" s="54">
         <v>4.1000000000000003E-3</v>
@@ -4790,31 +4790,31 @@
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D48" s="46" t="s">
         <v>42</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G48" s="46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I48" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J48" s="46" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K48" s="46" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L48" s="47">
         <v>2</v>
@@ -4827,7 +4827,7 @@
         <v>100</v>
       </c>
       <c r="O48" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P48" s="53">
         <v>1.4E-3</v>
@@ -4846,31 +4846,31 @@
         <v>40</v>
       </c>
       <c r="C49" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D49" s="50" t="s">
         <v>43</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G49" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I49" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J49" s="50" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K49" s="50" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L49" s="51">
         <v>1</v>
@@ -4883,7 +4883,7 @@
         <v>100</v>
       </c>
       <c r="O49" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P49" s="54">
         <v>2.2000000000000001E-3</v>
@@ -4902,31 +4902,31 @@
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G50" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H50" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="I50" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="J50" s="46" t="s">
         <v>373</v>
       </c>
-      <c r="H50" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="I50" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="J50" s="46" t="s">
-        <v>374</v>
-      </c>
       <c r="K50" s="46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L50" s="47">
         <v>1</v>
@@ -4939,7 +4939,7 @@
         <v>20</v>
       </c>
       <c r="O50" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P50" s="53">
         <v>2.5499999999999998E-2</v>
@@ -4958,31 +4958,31 @@
         <v>42</v>
       </c>
       <c r="C51" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D51" s="50" t="s">
         <v>45</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G51" s="50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J51" s="50" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K51" s="50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>100</v>
       </c>
       <c r="O51" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P51" s="54">
         <v>1.5E-3</v>
@@ -5014,31 +5014,31 @@
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D52" s="46" t="s">
         <v>46</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G52" s="46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I52" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J52" s="46" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K52" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L52" s="47">
         <v>1</v>
@@ -5051,7 +5051,7 @@
         <v>20</v>
       </c>
       <c r="O52" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P52" s="53">
         <v>3.7600000000000001E-2</v>
@@ -5070,31 +5070,31 @@
         <v>44</v>
       </c>
       <c r="C53" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D53" s="50" t="s">
         <v>47</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G53" s="50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J53" s="50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K53" s="50" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L53" s="51">
         <v>1</v>
@@ -5107,7 +5107,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P53" s="54">
         <v>1.8E-3</v>
@@ -5126,31 +5126,31 @@
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D54" s="46" t="s">
         <v>48</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F54" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G54" s="46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H54" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I54" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J54" s="46" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K54" s="46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L54" s="47">
         <v>2</v>
@@ -5163,7 +5163,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P54" s="53">
         <v>1.2999999999999999E-3</v>
@@ -5182,31 +5182,31 @@
         <v>46</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D55" s="50" t="s">
         <v>49</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G55" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J55" s="50" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K55" s="50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L55" s="51">
         <v>1</v>
@@ -5219,7 +5219,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P55" s="54">
         <v>1.2999999999999999E-3</v>
@@ -5238,31 +5238,31 @@
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D56" s="46" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G56" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="H56" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="I56" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="J56" s="46" t="s">
         <v>375</v>
       </c>
-      <c r="H56" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="I56" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="J56" s="46" t="s">
-        <v>376</v>
-      </c>
       <c r="K56" s="46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L56" s="47">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P56" s="53">
         <v>1.4E-3</v>
@@ -5294,31 +5294,31 @@
         <v>48</v>
       </c>
       <c r="C57" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D57" s="50" t="s">
-        <v>51</v>
+        <v>417</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G57" s="50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I57" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J57" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K57" s="50" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L57" s="51">
         <v>2</v>
@@ -5331,7 +5331,7 @@
         <v>40</v>
       </c>
       <c r="O57" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P57" s="54">
         <v>3.2899999999999999E-2</v>
@@ -5350,31 +5350,31 @@
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E58" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G58" s="69" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I58" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="J58" s="46" t="s">
         <v>389</v>
       </c>
-      <c r="J58" s="46" t="s">
-        <v>390</v>
-      </c>
       <c r="K58" s="46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L58" s="47">
         <v>4</v>
@@ -5387,7 +5387,7 @@
         <v>50</v>
       </c>
       <c r="O58" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P58" s="53">
         <v>7.1999999999999998E-3</v>
@@ -5406,29 +5406,29 @@
         <v>50</v>
       </c>
       <c r="C59" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D59" s="50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G59" s="50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I59" s="50"/>
       <c r="J59" s="50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K59" s="50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L59" s="51">
         <v>2</v>
@@ -5441,7 +5441,7 @@
         <v>40</v>
       </c>
       <c r="O59" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P59" s="54">
         <v>3.5499999999999997E-2</v>
@@ -5460,31 +5460,31 @@
         <v>51</v>
       </c>
       <c r="C60" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G60" s="46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H60" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J60" s="46" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K60" s="46" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L60" s="47">
         <v>1</v>
@@ -5497,7 +5497,7 @@
         <v>20</v>
       </c>
       <c r="O60" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P60" s="53">
         <v>3.9100000000000003E-2</v>
@@ -5516,29 +5516,29 @@
         <v>52</v>
       </c>
       <c r="C61" s="59" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D61" s="50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G61" s="50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H61" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I61" s="50"/>
       <c r="J61" s="50" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K61" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L61" s="51">
         <v>1</v>
@@ -5551,7 +5551,7 @@
         <v>50</v>
       </c>
       <c r="O61" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P61" s="54">
         <v>1.43E-2</v>
@@ -5570,29 +5570,29 @@
         <v>53</v>
       </c>
       <c r="C62" s="60" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D62" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F62" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G62" s="46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H62" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I62" s="46"/>
       <c r="J62" s="46" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K62" s="46" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L62" s="47">
         <v>2</v>
@@ -5605,7 +5605,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P62" s="53">
         <v>1E-3</v>
@@ -5624,31 +5624,31 @@
         <v>54</v>
       </c>
       <c r="C63" s="59" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" s="51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G63" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I63" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J63" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K63" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L63" s="51">
         <v>9</v>
@@ -5658,22 +5658,22 @@
         <v>90</v>
       </c>
       <c r="N63" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O63" s="63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P63" s="54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q63" s="54" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R63" s="64" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S63" s="52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5683,31 +5683,31 @@
         <v>55</v>
       </c>
       <c r="C64" s="60" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F64" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G64" s="46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H64" s="46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I64" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J64" s="46" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K64" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L64" s="47">
         <v>1</v>
@@ -5720,7 +5720,7 @@
         <v>20</v>
       </c>
       <c r="O64" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P64" s="53">
         <v>6.1899999999999997E-2</v>
@@ -5739,31 +5739,31 @@
         <v>56</v>
       </c>
       <c r="C65" s="59" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G65" s="50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H65" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I65" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J65" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K65" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L65" s="51">
         <v>1</v>
@@ -5776,7 +5776,7 @@
         <v>11</v>
       </c>
       <c r="O65" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P65" s="54">
         <v>1.9761</v>
@@ -5786,7 +5786,7 @@
         <v>21.737099999999998</v>
       </c>
       <c r="R65" s="64" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="S65" s="52"/>
     </row>
@@ -5797,31 +5797,31 @@
         <v>57</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F66" s="46" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G66" s="46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I66" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J66" s="46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K66" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L66" s="47">
         <v>1</v>
@@ -5834,7 +5834,7 @@
         <v>11</v>
       </c>
       <c r="O66" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P66" s="53">
         <v>0.4269</v>
@@ -5853,31 +5853,31 @@
         <v>58</v>
       </c>
       <c r="C67" s="59" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E67" s="51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G67" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I67" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J67" s="50" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K67" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L67" s="51">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         <v>11</v>
       </c>
       <c r="O67" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P67" s="54">
         <v>0.44240000000000002</v>
@@ -5909,31 +5909,31 @@
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G68" s="46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I68" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J68" s="46" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K68" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L68" s="47">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         <v>11</v>
       </c>
       <c r="O68" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P68" s="53">
         <v>1.6232</v>
@@ -5965,31 +5965,31 @@
         <v>60</v>
       </c>
       <c r="C69" s="59" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G69" s="50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I69" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J69" s="50" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K69" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L69" s="51">
         <v>1</v>
@@ -6002,7 +6002,7 @@
         <v>20</v>
       </c>
       <c r="O69" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P69" s="54">
         <v>5.6399999999999999E-2</v>
@@ -6021,31 +6021,31 @@
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G70" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H70" s="46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I70" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J70" s="46" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K70" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L70" s="47">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         <v>11</v>
       </c>
       <c r="O70" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P70" s="53">
         <v>3.9367000000000001</v>
@@ -6077,31 +6077,31 @@
         <v>62</v>
       </c>
       <c r="C71" s="59" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D71" s="50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E71" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G71" s="50" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H71" s="50" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I71" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J71" s="50" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L71" s="51">
         <v>1</v>
@@ -6114,7 +6114,7 @@
         <v>11</v>
       </c>
       <c r="O71" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P71" s="54">
         <v>0.94330000000000003</v>
@@ -6133,31 +6133,31 @@
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E72" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G72" s="46" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I72" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J72" s="46" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K72" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L72" s="47">
         <v>1</v>
@@ -6170,7 +6170,7 @@
         <v>11</v>
       </c>
       <c r="O72" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P72" s="53">
         <v>0.72819999999999996</v>
@@ -6189,31 +6189,31 @@
         <v>64</v>
       </c>
       <c r="C73" s="59" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D73" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G73" s="50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I73" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J73" s="50" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L73" s="51">
         <v>1</v>
@@ -6226,7 +6226,7 @@
         <v>11</v>
       </c>
       <c r="O73" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P73" s="54">
         <v>1.3220000000000001</v>
@@ -6245,31 +6245,31 @@
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D74" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E74" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G74" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H74" s="46" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I74" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J74" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K74" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L74" s="47">
         <v>1</v>
@@ -6282,7 +6282,7 @@
         <v>11</v>
       </c>
       <c r="O74" s="62" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P74" s="53">
         <v>1.1599999999999999</v>
@@ -6292,7 +6292,7 @@
         <v>12.76</v>
       </c>
       <c r="R74" s="72" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="S74" s="70"/>
     </row>
@@ -6303,31 +6303,31 @@
         <v>66</v>
       </c>
       <c r="C75" s="59" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D75" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E75" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G75" s="68">
         <v>4677</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I75" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="J75" s="50" t="s">
         <v>416</v>
       </c>
-      <c r="J75" s="50" t="s">
-        <v>417</v>
-      </c>
       <c r="K75" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L75" s="51">
         <v>1</v>
@@ -6340,7 +6340,7 @@
         <v>11</v>
       </c>
       <c r="O75" s="63" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P75" s="54">
         <v>2.7662</v>
@@ -6359,31 +6359,31 @@
         <v>67</v>
       </c>
       <c r="C76" s="60" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D76" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E76" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G76" s="46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I76" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K76" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L76" s="47">
         <v>1</v>
@@ -6396,7 +6396,7 @@
         <v>15</v>
       </c>
       <c r="O76" s="62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P76" s="53">
         <v>0.09</v>
@@ -6415,31 +6415,31 @@
         <v>68</v>
       </c>
       <c r="C77" s="59" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D77" s="50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E77" s="51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G77" s="50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H77" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I77" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J77" s="50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K77" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L77" s="51">
         <v>1</v>
@@ -6452,7 +6452,7 @@
         <v>15</v>
       </c>
       <c r="O77" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P77" s="54">
         <v>6.5100000000000005E-2</v>
@@ -6478,17 +6478,17 @@
       <c r="K78" s="37"/>
       <c r="L78" s="37"/>
       <c r="M78" s="37"/>
-      <c r="N78" s="82" t="s">
-        <v>406</v>
-      </c>
-      <c r="O78" s="83"/>
-      <c r="P78" s="83"/>
+      <c r="N78" s="86" t="s">
+        <v>405</v>
+      </c>
+      <c r="O78" s="87"/>
+      <c r="P78" s="87"/>
       <c r="Q78" s="66">
         <f>SUM(Q10:Q77)</f>
         <v>464.62409999999994</v>
       </c>
-      <c r="R78" s="78"/>
-      <c r="S78" s="79"/>
+      <c r="R78" s="82"/>
+      <c r="S78" s="83"/>
     </row>
     <row r="79" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -6504,17 +6504,17 @@
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
       <c r="M79" s="10"/>
-      <c r="N79" s="82" t="s">
-        <v>407</v>
-      </c>
-      <c r="O79" s="83"/>
-      <c r="P79" s="83"/>
+      <c r="N79" s="86" t="s">
+        <v>406</v>
+      </c>
+      <c r="O79" s="87"/>
+      <c r="P79" s="87"/>
       <c r="Q79" s="67">
         <f>Q78/10</f>
         <v>46.462409999999991</v>
       </c>
-      <c r="R79" s="80"/>
-      <c r="S79" s="81"/>
+      <c r="R79" s="84"/>
+      <c r="S79" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
+++ b/Deliverable/BOM/eSpark_Ezlo_Voice_Assistant_Node.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ezlo-VoiceAssistant\Deliverable\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DCB7D6-EDDB-4D01-8A3D-C99E7A3DE54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946BFCBB-576D-4930-ACF4-24504EE68884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="421">
   <si>
     <t>Component list</t>
   </si>
@@ -1016,9 +1016,6 @@
     <t>C96446</t>
   </si>
   <si>
-    <t>C519410</t>
-  </si>
-  <si>
     <t>C100042</t>
   </si>
   <si>
@@ -1037,9 +1034,6 @@
     <t>C5673</t>
   </si>
   <si>
-    <t>C282247</t>
-  </si>
-  <si>
     <t>C327022</t>
   </si>
   <si>
@@ -1100,9 +1094,6 @@
     <t>C967021</t>
   </si>
   <si>
-    <t>C62892</t>
-  </si>
-  <si>
     <t>C181312</t>
   </si>
   <si>
@@ -1163,12 +1154,6 @@
     <t>C100023</t>
   </si>
   <si>
-    <t>LCSC Stock= 10</t>
-  </si>
-  <si>
-    <t>LCSC Stock= 37</t>
-  </si>
-  <si>
     <t>C106203</t>
   </si>
   <si>
@@ -1284,6 +1269,30 @@
   </si>
   <si>
     <t>R20,R30</t>
+  </si>
+  <si>
+    <t>NON Stock In LCSC</t>
+  </si>
+  <si>
+    <t>CC0402JRNPO9BN220</t>
+  </si>
+  <si>
+    <t>0603CG101J250NT</t>
+  </si>
+  <si>
+    <t>C336627</t>
+  </si>
+  <si>
+    <t>0603CG2R7C500NT</t>
+  </si>
+  <si>
+    <t>C95180</t>
+  </si>
+  <si>
+    <t>C123008</t>
+  </si>
+  <si>
+    <t>UMH3NTN</t>
   </si>
 </sst>
 </file>
@@ -2435,7 +2444,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2460,7 +2469,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2485,7 +2494,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2656,7 +2665,7 @@
         <v>314</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>72</v>
@@ -2756,7 +2765,7 @@
         <v>4.43</v>
       </c>
       <c r="R11" s="64" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="S11" s="52"/>
     </row>
@@ -2813,9 +2822,7 @@
         <f t="shared" si="2"/>
         <v>10.680999999999999</v>
       </c>
-      <c r="R12" s="65" t="s">
-        <v>378</v>
-      </c>
+      <c r="R12" s="65"/>
       <c r="S12" s="48"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3004,17 +3011,17 @@
       <c r="F16" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="46" t="s">
+      <c r="G16" s="69" t="s">
         <v>184</v>
       </c>
       <c r="H16" s="46" t="s">
         <v>225</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>312</v>
+        <v>414</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="K16" s="46" t="s">
         <v>262</v>
@@ -3060,17 +3067,17 @@
       <c r="F17" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="G17" s="50" t="s">
+      <c r="G17" s="68" t="s">
         <v>185</v>
       </c>
       <c r="H17" s="50" t="s">
         <v>221</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>328</v>
+        <v>416</v>
       </c>
       <c r="K17" s="50" t="s">
         <v>263</v>
@@ -3089,11 +3096,11 @@
         <v>316</v>
       </c>
       <c r="P17" s="54">
-        <v>3.2000000000000002E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="Q17" s="54">
         <f t="shared" si="2"/>
-        <v>0.32</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="R17" s="64"/>
       <c r="S17" s="52"/>
@@ -3179,10 +3186,10 @@
         <v>226</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="K19" s="50" t="s">
         <v>265</v>
@@ -3238,7 +3245,7 @@
         <v>312</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K20" s="46" t="s">
         <v>266</v>
@@ -3294,7 +3301,7 @@
         <v>312</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K21" s="50" t="s">
         <v>267</v>
@@ -3350,7 +3357,7 @@
         <v>312</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K22" s="46" t="s">
         <v>268</v>
@@ -3406,7 +3413,7 @@
         <v>312</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K23" s="50" t="s">
         <v>260</v>
@@ -3462,7 +3469,7 @@
         <v>312</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K24" s="46" t="s">
         <v>260</v>
@@ -3515,10 +3522,10 @@
         <v>224</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="K25" s="50" t="s">
         <v>269</v>
@@ -3556,7 +3563,7 @@
         <v>314</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E26" s="47" t="s">
         <v>78</v>
@@ -3574,7 +3581,7 @@
         <v>312</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K26" s="46" t="s">
         <v>261</v>
@@ -3620,17 +3627,17 @@
       <c r="F27" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="G27" s="50" t="s">
+      <c r="G27" s="68" t="s">
         <v>194</v>
       </c>
       <c r="H27" s="50" t="s">
         <v>221</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>312</v>
+        <v>417</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>335</v>
+        <v>418</v>
       </c>
       <c r="K27" s="50" t="s">
         <v>270</v>
@@ -3643,17 +3650,17 @@
         <v>10</v>
       </c>
       <c r="N27" s="50">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O27" s="63" t="s">
         <v>316</v>
       </c>
       <c r="P27" s="54">
-        <v>6.7000000000000002E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="Q27" s="54">
         <f t="shared" si="2"/>
-        <v>0.33500000000000002</v>
+        <v>0.32</v>
       </c>
       <c r="R27" s="64"/>
       <c r="S27" s="52"/>
@@ -3686,7 +3693,7 @@
         <v>312</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K28" s="46" t="s">
         <v>271</v>
@@ -3724,7 +3731,7 @@
         <v>314</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="E29" s="51" t="s">
         <v>91</v>
@@ -3739,10 +3746,10 @@
         <v>221</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="J29" s="50" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="K29" s="50" t="s">
         <v>272</v>
@@ -3798,7 +3805,7 @@
         <v>312</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="K30" s="46" t="s">
         <v>312</v>
@@ -3842,7 +3849,7 @@
         <v>93</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G31" s="50" t="s">
         <v>149</v>
@@ -3854,7 +3861,7 @@
         <v>312</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K31" s="50" t="s">
         <v>312</v>
@@ -3945,7 +3952,7 @@
         <v>24</v>
       </c>
       <c r="C33" s="59" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D33" s="50" t="s">
         <v>27</v>
@@ -4001,7 +4008,7 @@
         <v>25</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D34" s="46" t="s">
         <v>28</v>
@@ -4019,10 +4026,10 @@
         <v>234</v>
       </c>
       <c r="I34" s="46" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="K34" s="46" t="s">
         <v>312</v>
@@ -4057,7 +4064,7 @@
         <v>26</v>
       </c>
       <c r="C35" s="59" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D35" s="50" t="s">
         <v>29</v>
@@ -4113,7 +4120,7 @@
         <v>27</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D36" s="46" t="s">
         <v>30</v>
@@ -4134,7 +4141,7 @@
         <v>312</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K36" s="46" t="s">
         <v>274</v>
@@ -4169,7 +4176,7 @@
         <v>28</v>
       </c>
       <c r="C37" s="59" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D37" s="50" t="s">
         <v>31</v>
@@ -4190,7 +4197,7 @@
         <v>312</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K37" s="50" t="s">
         <v>275</v>
@@ -4225,7 +4232,7 @@
         <v>29</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D38" s="46" t="s">
         <v>32</v>
@@ -4237,16 +4244,16 @@
         <v>156</v>
       </c>
       <c r="G38" s="46" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I38" s="46" t="s">
         <v>312</v>
       </c>
       <c r="J38" s="46" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K38" s="46" t="s">
         <v>276</v>
@@ -4281,7 +4288,7 @@
         <v>30</v>
       </c>
       <c r="C39" s="59" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D39" s="50" t="s">
         <v>33</v>
@@ -4302,7 +4309,7 @@
         <v>312</v>
       </c>
       <c r="J39" s="50" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="K39" s="50" t="s">
         <v>277</v>
@@ -4337,7 +4344,7 @@
         <v>31</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D40" s="46" t="s">
         <v>34</v>
@@ -4358,7 +4365,7 @@
         <v>312</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="K40" s="46" t="s">
         <v>278</v>
@@ -4393,7 +4400,7 @@
         <v>32</v>
       </c>
       <c r="C41" s="59" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D41" s="50" t="s">
         <v>35</v>
@@ -4414,7 +4421,7 @@
         <v>312</v>
       </c>
       <c r="J41" s="50" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K41" s="50" t="s">
         <v>312</v>
@@ -4449,7 +4456,7 @@
         <v>33</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D42" s="46" t="s">
         <v>36</v>
@@ -4486,7 +4493,7 @@
         <v>80</v>
       </c>
       <c r="O42" s="62" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="P42" s="53">
         <v>2.9</v>
@@ -4496,7 +4503,7 @@
         <v>232</v>
       </c>
       <c r="R42" s="65" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="S42" s="70"/>
     </row>
@@ -4507,7 +4514,7 @@
         <v>34</v>
       </c>
       <c r="C43" s="59" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D43" s="50" t="s">
         <v>37</v>
@@ -4525,10 +4532,10 @@
         <v>241</v>
       </c>
       <c r="I43" s="50" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J43" s="50" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="K43" s="50" t="s">
         <v>312</v>
@@ -4563,7 +4570,7 @@
         <v>35</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D44" s="46" t="s">
         <v>38</v>
@@ -4581,10 +4588,10 @@
         <v>241</v>
       </c>
       <c r="I44" s="46" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="J44" s="46" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="K44" s="46" t="s">
         <v>312</v>
@@ -4619,7 +4626,7 @@
         <v>36</v>
       </c>
       <c r="C45" s="59" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D45" s="50" t="s">
         <v>39</v>
@@ -4678,7 +4685,7 @@
         <v>37</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D46" s="46" t="s">
         <v>40</v>
@@ -4734,7 +4741,7 @@
         <v>38</v>
       </c>
       <c r="C47" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D47" s="50" t="s">
         <v>41</v>
@@ -4746,7 +4753,7 @@
         <v>162</v>
       </c>
       <c r="G47" s="50" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H47" s="50" t="s">
         <v>242</v>
@@ -4755,7 +4762,7 @@
         <v>312</v>
       </c>
       <c r="J47" s="50" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="K47" s="50" t="s">
         <v>280</v>
@@ -4790,7 +4797,7 @@
         <v>39</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D48" s="46" t="s">
         <v>42</v>
@@ -4811,7 +4818,7 @@
         <v>312</v>
       </c>
       <c r="J48" s="46" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="K48" s="46" t="s">
         <v>281</v>
@@ -4846,7 +4853,7 @@
         <v>40</v>
       </c>
       <c r="C49" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D49" s="50" t="s">
         <v>43</v>
@@ -4867,7 +4874,7 @@
         <v>312</v>
       </c>
       <c r="J49" s="50" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K49" s="50" t="s">
         <v>282</v>
@@ -4902,7 +4909,7 @@
         <v>41</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>44</v>
@@ -4914,7 +4921,7 @@
         <v>163</v>
       </c>
       <c r="G50" s="46" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H50" s="46" t="s">
         <v>244</v>
@@ -4923,7 +4930,7 @@
         <v>312</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K50" s="46" t="s">
         <v>283</v>
@@ -4958,7 +4965,7 @@
         <v>42</v>
       </c>
       <c r="C51" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D51" s="50" t="s">
         <v>45</v>
@@ -4979,7 +4986,7 @@
         <v>312</v>
       </c>
       <c r="J51" s="50" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K51" s="50" t="s">
         <v>284</v>
@@ -5014,7 +5021,7 @@
         <v>43</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D52" s="46" t="s">
         <v>46</v>
@@ -5035,7 +5042,7 @@
         <v>312</v>
       </c>
       <c r="J52" s="46" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K52" s="46" t="s">
         <v>285</v>
@@ -5070,7 +5077,7 @@
         <v>44</v>
       </c>
       <c r="C53" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D53" s="50" t="s">
         <v>47</v>
@@ -5091,7 +5098,7 @@
         <v>312</v>
       </c>
       <c r="J53" s="50" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K53" s="50" t="s">
         <v>286</v>
@@ -5126,7 +5133,7 @@
         <v>45</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D54" s="46" t="s">
         <v>48</v>
@@ -5147,7 +5154,7 @@
         <v>312</v>
       </c>
       <c r="J54" s="46" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K54" s="46" t="s">
         <v>287</v>
@@ -5182,7 +5189,7 @@
         <v>46</v>
       </c>
       <c r="C55" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D55" s="50" t="s">
         <v>49</v>
@@ -5203,7 +5210,7 @@
         <v>312</v>
       </c>
       <c r="J55" s="50" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="K55" s="50" t="s">
         <v>288</v>
@@ -5238,7 +5245,7 @@
         <v>47</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D56" s="46" t="s">
         <v>50</v>
@@ -5250,7 +5257,7 @@
         <v>162</v>
       </c>
       <c r="G56" s="46" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H56" s="46" t="s">
         <v>221</v>
@@ -5259,7 +5266,7 @@
         <v>312</v>
       </c>
       <c r="J56" s="46" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K56" s="46" t="s">
         <v>289</v>
@@ -5294,10 +5301,10 @@
         <v>48</v>
       </c>
       <c r="C57" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D57" s="50" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E57" s="51" t="s">
         <v>119</v>
@@ -5350,7 +5357,7 @@
         <v>49</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D58" s="46" t="s">
         <v>51</v>
@@ -5368,10 +5375,10 @@
         <v>221</v>
       </c>
       <c r="I58" s="46" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J58" s="46" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="K58" s="46" t="s">
         <v>291</v>
@@ -5406,7 +5413,7 @@
         <v>50</v>
       </c>
       <c r="C59" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D59" s="50" t="s">
         <v>52</v>
@@ -5425,7 +5432,7 @@
       </c>
       <c r="I59" s="50"/>
       <c r="J59" s="50" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K59" s="50" t="s">
         <v>292</v>
@@ -5460,7 +5467,7 @@
         <v>51</v>
       </c>
       <c r="C60" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D60" s="46" t="s">
         <v>53</v>
@@ -5481,7 +5488,7 @@
         <v>312</v>
       </c>
       <c r="J60" s="46" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K60" s="46" t="s">
         <v>293</v>
@@ -5516,7 +5523,7 @@
         <v>52</v>
       </c>
       <c r="C61" s="59" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D61" s="50" t="s">
         <v>54</v>
@@ -5535,7 +5542,7 @@
       </c>
       <c r="I61" s="50"/>
       <c r="J61" s="50" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K61" s="50" t="s">
         <v>294</v>
@@ -5570,7 +5577,7 @@
         <v>53</v>
       </c>
       <c r="C62" s="60" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D62" s="46" t="s">
         <v>55</v>
@@ -5589,7 +5596,7 @@
       </c>
       <c r="I62" s="46"/>
       <c r="J62" s="46" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="K62" s="46" t="s">
         <v>295</v>
@@ -5683,7 +5690,7 @@
         <v>55</v>
       </c>
       <c r="C64" s="60" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D64" s="46" t="s">
         <v>57</v>
@@ -5704,7 +5711,7 @@
         <v>312</v>
       </c>
       <c r="J64" s="46" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K64" s="46" t="s">
         <v>312</v>
@@ -5739,7 +5746,7 @@
         <v>56</v>
       </c>
       <c r="C65" s="59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D65" s="50" t="s">
         <v>58</v>
@@ -5760,7 +5767,7 @@
         <v>312</v>
       </c>
       <c r="J65" s="50" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="K65" s="50" t="s">
         <v>312</v>
@@ -5786,7 +5793,7 @@
         <v>21.737099999999998</v>
       </c>
       <c r="R65" s="64" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="S65" s="52"/>
     </row>
@@ -5797,7 +5804,7 @@
         <v>57</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D66" s="46" t="s">
         <v>59</v>
@@ -5818,7 +5825,7 @@
         <v>312</v>
       </c>
       <c r="J66" s="46" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K66" s="46" t="s">
         <v>312</v>
@@ -5853,7 +5860,7 @@
         <v>58</v>
       </c>
       <c r="C67" s="59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D67" s="50" t="s">
         <v>60</v>
@@ -5862,7 +5869,7 @@
         <v>129</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G67" s="50" t="s">
         <v>169</v>
@@ -5874,7 +5881,7 @@
         <v>312</v>
       </c>
       <c r="J67" s="50" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K67" s="50" t="s">
         <v>312</v>
@@ -5909,7 +5916,7 @@
         <v>59</v>
       </c>
       <c r="C68" s="60" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D68" s="46" t="s">
         <v>61</v>
@@ -5930,7 +5937,7 @@
         <v>312</v>
       </c>
       <c r="J68" s="46" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K68" s="46" t="s">
         <v>312</v>
@@ -5965,7 +5972,7 @@
         <v>60</v>
       </c>
       <c r="C69" s="59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D69" s="50" t="s">
         <v>62</v>
@@ -5976,17 +5983,17 @@
       <c r="F69" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="G69" s="50" t="s">
+      <c r="G69" s="68" t="s">
         <v>171</v>
       </c>
       <c r="H69" s="50" t="s">
         <v>249</v>
       </c>
       <c r="I69" s="50" t="s">
-        <v>312</v>
+        <v>420</v>
       </c>
       <c r="J69" s="50" t="s">
-        <v>356</v>
+        <v>419</v>
       </c>
       <c r="K69" s="50" t="s">
         <v>312</v>
@@ -5999,17 +6006,17 @@
         <v>10</v>
       </c>
       <c r="N69" s="50">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O69" s="63" t="s">
         <v>316</v>
       </c>
       <c r="P69" s="54">
-        <v>5.6399999999999999E-2</v>
+        <v>6.5299999999999997E-2</v>
       </c>
       <c r="Q69" s="54">
         <f t="shared" ref="Q69:Q77" si="4">P69*N69</f>
-        <v>1.1279999999999999</v>
+        <v>0.97949999999999993</v>
       </c>
       <c r="R69" s="64"/>
       <c r="S69" s="52"/>
@@ -6021,7 +6028,7 @@
         <v>61</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D70" s="46" t="s">
         <v>63</v>
@@ -6030,7 +6037,7 @@
         <v>132</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G70" s="46" t="s">
         <v>172</v>
@@ -6042,7 +6049,7 @@
         <v>312</v>
       </c>
       <c r="J70" s="46" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="K70" s="46" t="s">
         <v>312</v>
@@ -6077,7 +6084,7 @@
         <v>62</v>
       </c>
       <c r="C71" s="59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D71" s="50" t="s">
         <v>64</v>
@@ -6098,7 +6105,7 @@
         <v>312</v>
       </c>
       <c r="J71" s="50" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="K71" s="50" t="s">
         <v>312</v>
@@ -6133,7 +6140,7 @@
         <v>63</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D72" s="46" t="s">
         <v>65</v>
@@ -6154,7 +6161,7 @@
         <v>312</v>
       </c>
       <c r="J72" s="46" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="K72" s="46" t="s">
         <v>312</v>
@@ -6189,7 +6196,7 @@
         <v>64</v>
       </c>
       <c r="C73" s="59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D73" s="50" t="s">
         <v>66</v>
@@ -6210,7 +6217,7 @@
         <v>312</v>
       </c>
       <c r="J73" s="50" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="K73" s="50" t="s">
         <v>312</v>
@@ -6245,7 +6252,7 @@
         <v>65</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D74" s="46" t="s">
         <v>67</v>
@@ -6282,7 +6289,7 @@
         <v>11</v>
       </c>
       <c r="O74" s="62" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="P74" s="53">
         <v>1.1599999999999999</v>
@@ -6292,7 +6299,7 @@
         <v>12.76</v>
       </c>
       <c r="R74" s="72" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="S74" s="70"/>
     </row>
@@ -6303,7 +6310,7 @@
         <v>66</v>
       </c>
       <c r="C75" s="59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D75" s="50" t="s">
         <v>68</v>
@@ -6321,10 +6328,10 @@
         <v>252</v>
       </c>
       <c r="I75" s="50" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="J75" s="50" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="K75" s="50" t="s">
         <v>312</v>
@@ -6340,7 +6347,7 @@
         <v>11</v>
       </c>
       <c r="O75" s="63" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="P75" s="54">
         <v>2.7662</v>
@@ -6359,7 +6366,7 @@
         <v>67</v>
       </c>
       <c r="C76" s="60" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D76" s="46" t="s">
         <v>69</v>
@@ -6380,7 +6387,7 @@
         <v>312</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="K76" s="46" t="s">
         <v>296</v>
@@ -6415,7 +6422,7 @@
         <v>68</v>
       </c>
       <c r="C77" s="59" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D77" s="50" t="s">
         <v>70</v>
@@ -6436,7 +6443,7 @@
         <v>312</v>
       </c>
       <c r="J77" s="50" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="K77" s="50" t="s">
         <v>297</v>
@@ -6479,13 +6486,13 @@
       <c r="L78" s="37"/>
       <c r="M78" s="37"/>
       <c r="N78" s="86" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="O78" s="87"/>
       <c r="P78" s="87"/>
       <c r="Q78" s="66">
         <f>SUM(Q10:Q77)</f>
-        <v>464.62409999999994</v>
+        <v>464.48059999999992</v>
       </c>
       <c r="R78" s="82"/>
       <c r="S78" s="83"/>
@@ -6505,13 +6512,13 @@
       <c r="L79" s="10"/>
       <c r="M79" s="10"/>
       <c r="N79" s="86" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="O79" s="87"/>
       <c r="P79" s="87"/>
       <c r="Q79" s="67">
         <f>Q78/10</f>
-        <v>46.462409999999991</v>
+        <v>46.448059999999991</v>
       </c>
       <c r="R79" s="84"/>
       <c r="S79" s="85"/>
@@ -6535,59 +6542,59 @@
     <hyperlink ref="O13" r:id="rId8" xr:uid="{D4E1EC75-7F56-4D22-ADA6-CFE6FFC1872F}"/>
     <hyperlink ref="O14" r:id="rId9" xr:uid="{226D0111-5B69-4FBA-8572-1B5BC54DAFE8}"/>
     <hyperlink ref="O15" r:id="rId10" xr:uid="{285211AF-882C-4DEA-8FA4-BA4D841106DE}"/>
-    <hyperlink ref="O17" r:id="rId11" xr:uid="{2DE4352B-08D1-4CFA-AFBD-8531C9B58500}"/>
-    <hyperlink ref="O20" r:id="rId12" xr:uid="{B4CDEF8B-CEC7-43A0-A9F6-56EAEEDDBE24}"/>
-    <hyperlink ref="O21" r:id="rId13" xr:uid="{2CEE3725-F70A-451E-A380-7511EA16061C}"/>
-    <hyperlink ref="O22" r:id="rId14" xr:uid="{5862839D-C5EC-4A40-934C-A9C57E4BECC7}"/>
-    <hyperlink ref="O23" r:id="rId15" xr:uid="{7B04A431-944E-4A4A-997B-EC4F1D76DC6B}"/>
-    <hyperlink ref="O24" r:id="rId16" xr:uid="{DA9E30EA-7990-4FA1-A832-0FDE709D02A1}"/>
-    <hyperlink ref="O26" r:id="rId17" xr:uid="{335E1895-5860-4841-A6ED-952BDA93085A}"/>
-    <hyperlink ref="O27" r:id="rId18" xr:uid="{06D36592-DA49-4ABF-B5C9-1D3B86FE13B5}"/>
-    <hyperlink ref="O28" r:id="rId19" xr:uid="{8F178DE8-2DD2-4D57-BE91-D1E745FFEB73}"/>
-    <hyperlink ref="O30" r:id="rId20" xr:uid="{9FFDFF22-06D8-4ED4-8A9B-DFB2463CDC89}"/>
-    <hyperlink ref="O31" r:id="rId21" xr:uid="{16D6D382-09C3-4775-AAAA-FC0295F78BB3}"/>
-    <hyperlink ref="O36" r:id="rId22" xr:uid="{E5E4CFE6-BE6E-478D-A1CF-E49BA204E382}"/>
-    <hyperlink ref="O37" r:id="rId23" xr:uid="{6E6C19CB-15D1-44AB-9917-75FCAAE2FD24}"/>
-    <hyperlink ref="O39" r:id="rId24" xr:uid="{29B7F5E8-2DFF-44D7-B091-DCEFE06E7C83}"/>
-    <hyperlink ref="O40" r:id="rId25" xr:uid="{E0C9FF27-6C36-4E03-AD5E-39435BA180EA}"/>
-    <hyperlink ref="O41" r:id="rId26" xr:uid="{4312D63B-0298-4960-B515-771D3E8B85CC}"/>
-    <hyperlink ref="O43" r:id="rId27" xr:uid="{CF9E712A-1F1E-4155-8BD6-0FC723B65B14}"/>
-    <hyperlink ref="O44" r:id="rId28" xr:uid="{7821C627-2282-46BB-93D0-B1552EBB9F32}"/>
-    <hyperlink ref="O47" r:id="rId29" xr:uid="{6B13A082-931D-4827-A6EA-6926CBA6F3BC}"/>
-    <hyperlink ref="O48" r:id="rId30" xr:uid="{C9F96F3A-83DA-4020-A58D-B9C104DC2244}"/>
-    <hyperlink ref="O49" r:id="rId31" xr:uid="{FA5D3023-C28E-4920-B034-33DE5733A921}"/>
-    <hyperlink ref="O50" r:id="rId32" xr:uid="{45A28338-E148-40B1-8F40-9F443D5C5ECA}"/>
-    <hyperlink ref="O51" r:id="rId33" xr:uid="{80DE6F5E-FB37-4FEA-9AB6-9CF3D331F4C1}"/>
-    <hyperlink ref="O52" r:id="rId34" xr:uid="{442E387C-4D86-402D-BF2B-D77E70F21A89}"/>
-    <hyperlink ref="O53" r:id="rId35" xr:uid="{7A6416FE-6364-440A-8274-C7D7C254C268}"/>
-    <hyperlink ref="O54" r:id="rId36" xr:uid="{41C4DFCD-099A-40C0-92E5-1EC972C0E694}"/>
-    <hyperlink ref="O55" r:id="rId37" xr:uid="{8387B773-ABF8-4F4A-8895-EC0BBF8ED49A}"/>
-    <hyperlink ref="O56" r:id="rId38" xr:uid="{02DA634D-BB35-4D56-A91A-9B93D2A8094A}"/>
-    <hyperlink ref="O59" r:id="rId39" xr:uid="{D95DD3AC-48E1-4E24-9501-32AC06BA6AE4}"/>
-    <hyperlink ref="O60" r:id="rId40" xr:uid="{8734B2D7-3FEB-43C7-99CD-0001A66A385D}"/>
-    <hyperlink ref="O61" r:id="rId41" xr:uid="{3B8B5D5C-5A16-467A-88FA-616A9AECDA72}"/>
-    <hyperlink ref="O62" r:id="rId42" xr:uid="{5285C8FA-C754-43F5-975E-F2E4D890D95B}"/>
-    <hyperlink ref="O64" r:id="rId43" xr:uid="{316BA8C0-A938-4C50-9743-985F8C76544D}"/>
-    <hyperlink ref="O66" r:id="rId44" xr:uid="{3F8213FD-C01B-4447-91D9-4E057269745D}"/>
-    <hyperlink ref="O67" r:id="rId45" xr:uid="{4B7B4791-27F1-4299-A5B6-C71DB36769D0}"/>
-    <hyperlink ref="O68" r:id="rId46" xr:uid="{B61AFFC2-D62C-447B-B59C-8B33FDC28A19}"/>
-    <hyperlink ref="O69" r:id="rId47" xr:uid="{718AC0C2-915D-4181-ACDC-07D2A1F6A0B7}"/>
-    <hyperlink ref="O70" r:id="rId48" xr:uid="{18D79EB6-DE50-46AB-BB44-09F676D4AA6C}"/>
-    <hyperlink ref="O71" r:id="rId49" xr:uid="{B4F980DB-7127-4AB1-A41E-88F26338262F}"/>
-    <hyperlink ref="O72" r:id="rId50" xr:uid="{3836B695-E401-46D4-A238-E31716D58B39}"/>
-    <hyperlink ref="O73" r:id="rId51" xr:uid="{C5515060-E999-4D3D-B0E1-6DCE2168A002}"/>
-    <hyperlink ref="O77" r:id="rId52" xr:uid="{0C8FCE85-9E44-400B-B214-A57E5DC2AE74}"/>
-    <hyperlink ref="O76" r:id="rId53" xr:uid="{EA4D8B3E-B1C4-476C-A93D-AF10A1C5CEA9}"/>
-    <hyperlink ref="O11" r:id="rId54" xr:uid="{CB961B6A-D153-4513-B95E-8947C1F67452}"/>
-    <hyperlink ref="O12" r:id="rId55" xr:uid="{5DEB9260-0ACF-4732-B3F1-378713AA6CFD}"/>
-    <hyperlink ref="O16" r:id="rId56" xr:uid="{B6BA4ED4-B2FB-4E47-8D3B-9201C9619465}"/>
-    <hyperlink ref="O19" r:id="rId57" xr:uid="{2C744A7C-ED0B-4D7B-A324-CC70807A090B}"/>
-    <hyperlink ref="O29" r:id="rId58" xr:uid="{A0553738-8D52-4CD3-9B03-F88F5C89C901}"/>
-    <hyperlink ref="O34" r:id="rId59" xr:uid="{3B4FD01B-0158-4755-B556-199DD4A4F21C}"/>
-    <hyperlink ref="O38" r:id="rId60" xr:uid="{FBA2F3AF-4786-4158-9B8B-155F2E99379A}"/>
-    <hyperlink ref="O58" r:id="rId61" xr:uid="{014E192F-4F33-4E08-ACE2-4778AE694DE9}"/>
-    <hyperlink ref="O65" r:id="rId62" xr:uid="{EB66FF4B-A503-4BDC-8DEC-B0329A0FF9C7}"/>
-    <hyperlink ref="O25" r:id="rId63" xr:uid="{CFCD8C6D-2653-4D9C-9250-2514B1905C07}"/>
+    <hyperlink ref="O20" r:id="rId11" xr:uid="{B4CDEF8B-CEC7-43A0-A9F6-56EAEEDDBE24}"/>
+    <hyperlink ref="O21" r:id="rId12" xr:uid="{2CEE3725-F70A-451E-A380-7511EA16061C}"/>
+    <hyperlink ref="O22" r:id="rId13" xr:uid="{5862839D-C5EC-4A40-934C-A9C57E4BECC7}"/>
+    <hyperlink ref="O23" r:id="rId14" xr:uid="{7B04A431-944E-4A4A-997B-EC4F1D76DC6B}"/>
+    <hyperlink ref="O24" r:id="rId15" xr:uid="{DA9E30EA-7990-4FA1-A832-0FDE709D02A1}"/>
+    <hyperlink ref="O26" r:id="rId16" xr:uid="{335E1895-5860-4841-A6ED-952BDA93085A}"/>
+    <hyperlink ref="O28" r:id="rId17" xr:uid="{8F178DE8-2DD2-4D57-BE91-D1E745FFEB73}"/>
+    <hyperlink ref="O30" r:id="rId18" xr:uid="{9FFDFF22-06D8-4ED4-8A9B-DFB2463CDC89}"/>
+    <hyperlink ref="O31" r:id="rId19" xr:uid="{16D6D382-09C3-4775-AAAA-FC0295F78BB3}"/>
+    <hyperlink ref="O36" r:id="rId20" xr:uid="{E5E4CFE6-BE6E-478D-A1CF-E49BA204E382}"/>
+    <hyperlink ref="O37" r:id="rId21" xr:uid="{6E6C19CB-15D1-44AB-9917-75FCAAE2FD24}"/>
+    <hyperlink ref="O39" r:id="rId22" xr:uid="{29B7F5E8-2DFF-44D7-B091-DCEFE06E7C83}"/>
+    <hyperlink ref="O40" r:id="rId23" xr:uid="{E0C9FF27-6C36-4E03-AD5E-39435BA180EA}"/>
+    <hyperlink ref="O41" r:id="rId24" xr:uid="{4312D63B-0298-4960-B515-771D3E8B85CC}"/>
+    <hyperlink ref="O43" r:id="rId25" xr:uid="{CF9E712A-1F1E-4155-8BD6-0FC723B65B14}"/>
+    <hyperlink ref="O44" r:id="rId26" xr:uid="{7821C627-2282-46BB-93D0-B1552EBB9F32}"/>
+    <hyperlink ref="O47" r:id="rId27" xr:uid="{6B13A082-931D-4827-A6EA-6926CBA6F3BC}"/>
+    <hyperlink ref="O48" r:id="rId28" xr:uid="{C9F96F3A-83DA-4020-A58D-B9C104DC2244}"/>
+    <hyperlink ref="O49" r:id="rId29" xr:uid="{FA5D3023-C28E-4920-B034-33DE5733A921}"/>
+    <hyperlink ref="O50" r:id="rId30" xr:uid="{45A28338-E148-40B1-8F40-9F443D5C5ECA}"/>
+    <hyperlink ref="O51" r:id="rId31" xr:uid="{80DE6F5E-FB37-4FEA-9AB6-9CF3D331F4C1}"/>
+    <hyperlink ref="O52" r:id="rId32" xr:uid="{442E387C-4D86-402D-BF2B-D77E70F21A89}"/>
+    <hyperlink ref="O53" r:id="rId33" xr:uid="{7A6416FE-6364-440A-8274-C7D7C254C268}"/>
+    <hyperlink ref="O54" r:id="rId34" xr:uid="{41C4DFCD-099A-40C0-92E5-1EC972C0E694}"/>
+    <hyperlink ref="O55" r:id="rId35" xr:uid="{8387B773-ABF8-4F4A-8895-EC0BBF8ED49A}"/>
+    <hyperlink ref="O56" r:id="rId36" xr:uid="{02DA634D-BB35-4D56-A91A-9B93D2A8094A}"/>
+    <hyperlink ref="O59" r:id="rId37" xr:uid="{D95DD3AC-48E1-4E24-9501-32AC06BA6AE4}"/>
+    <hyperlink ref="O60" r:id="rId38" xr:uid="{8734B2D7-3FEB-43C7-99CD-0001A66A385D}"/>
+    <hyperlink ref="O61" r:id="rId39" xr:uid="{3B8B5D5C-5A16-467A-88FA-616A9AECDA72}"/>
+    <hyperlink ref="O62" r:id="rId40" xr:uid="{5285C8FA-C754-43F5-975E-F2E4D890D95B}"/>
+    <hyperlink ref="O64" r:id="rId41" xr:uid="{316BA8C0-A938-4C50-9743-985F8C76544D}"/>
+    <hyperlink ref="O66" r:id="rId42" xr:uid="{3F8213FD-C01B-4447-91D9-4E057269745D}"/>
+    <hyperlink ref="O67" r:id="rId43" xr:uid="{4B7B4791-27F1-4299-A5B6-C71DB36769D0}"/>
+    <hyperlink ref="O68" r:id="rId44" xr:uid="{B61AFFC2-D62C-447B-B59C-8B33FDC28A19}"/>
+    <hyperlink ref="O70" r:id="rId45" xr:uid="{18D79EB6-DE50-46AB-BB44-09F676D4AA6C}"/>
+    <hyperlink ref="O71" r:id="rId46" xr:uid="{B4F980DB-7127-4AB1-A41E-88F26338262F}"/>
+    <hyperlink ref="O72" r:id="rId47" xr:uid="{3836B695-E401-46D4-A238-E31716D58B39}"/>
+    <hyperlink ref="O73" r:id="rId48" xr:uid="{C5515060-E999-4D3D-B0E1-6DCE2168A002}"/>
+    <hyperlink ref="O77" r:id="rId49" xr:uid="{0C8FCE85-9E44-400B-B214-A57E5DC2AE74}"/>
+    <hyperlink ref="O76" r:id="rId50" xr:uid="{EA4D8B3E-B1C4-476C-A93D-AF10A1C5CEA9}"/>
+    <hyperlink ref="O11" r:id="rId51" xr:uid="{CB961B6A-D153-4513-B95E-8947C1F67452}"/>
+    <hyperlink ref="O12" r:id="rId52" xr:uid="{5DEB9260-0ACF-4732-B3F1-378713AA6CFD}"/>
+    <hyperlink ref="O16" r:id="rId53" xr:uid="{B6BA4ED4-B2FB-4E47-8D3B-9201C9619465}"/>
+    <hyperlink ref="O19" r:id="rId54" xr:uid="{2C744A7C-ED0B-4D7B-A324-CC70807A090B}"/>
+    <hyperlink ref="O29" r:id="rId55" xr:uid="{A0553738-8D52-4CD3-9B03-F88F5C89C901}"/>
+    <hyperlink ref="O34" r:id="rId56" xr:uid="{3B4FD01B-0158-4755-B556-199DD4A4F21C}"/>
+    <hyperlink ref="O38" r:id="rId57" xr:uid="{FBA2F3AF-4786-4158-9B8B-155F2E99379A}"/>
+    <hyperlink ref="O58" r:id="rId58" xr:uid="{014E192F-4F33-4E08-ACE2-4778AE694DE9}"/>
+    <hyperlink ref="O65" r:id="rId59" xr:uid="{EB66FF4B-A503-4BDC-8DEC-B0329A0FF9C7}"/>
+    <hyperlink ref="O25" r:id="rId60" xr:uid="{CFCD8C6D-2653-4D9C-9250-2514B1905C07}"/>
+    <hyperlink ref="O17" r:id="rId61" xr:uid="{25A03139-8E7E-4A2E-A666-E7ADD02C774D}"/>
+    <hyperlink ref="O27" r:id="rId62" xr:uid="{DB07E97C-F1E2-4E41-B752-DB40DCF69375}"/>
+    <hyperlink ref="O69" r:id="rId63" xr:uid="{859B90C6-3417-4391-B013-B67DC6ECC731}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId64"/>
